--- a/data/macro/USA/USGDP.xlsx
+++ b/data/macro/USA/USGDP.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A819ECF2-D1FD-44E2-ACCA-F37C224679B4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FE2BD7-832F-4B59-A348-892FB48AE6F9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" xr2:uid="{DF730CA5-B386-4F44-87DF-4B36E64B9A15}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="12">
   <si>
     <t>Release Date</t>
   </si>
@@ -72,13 +72,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="177" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="180" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+  <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="181" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="182" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -107,6 +108,19 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -125,47 +139,60 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="백분율" xfId="2" builtinId="5"/>
     <cellStyle name="쉼표" xfId="1" builtinId="3"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -479,14 +506,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00FCE0E7-6C64-48A0-8BF6-812467A264DB}">
-  <dimension ref="A1:H212"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H214"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="14.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -496,5295 +526,5344 @@
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+      <c r="A2" s="8">
         <v>39447</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="8">
         <v>39506</v>
       </c>
-      <c r="C2" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1">
+      <c r="C2" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="12">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="12">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="12">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="A3" s="8">
         <v>39447</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="8">
         <v>39534</v>
       </c>
-      <c r="C3" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="C3" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="12">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="12">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="12">
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="A4" s="8">
         <v>39538</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="8">
         <v>39568</v>
       </c>
-      <c r="C4" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="C4" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="12">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="12">
         <v>2E-3</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="12">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="A5" s="8">
         <v>39538</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="8">
         <v>39625</v>
       </c>
-      <c r="C5" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="1">
+      <c r="C5" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="12">
         <v>2.7E-2</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="12">
         <v>0.01</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="12">
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="A6" s="8">
         <v>39629</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="8">
         <v>39660</v>
       </c>
-      <c r="C6" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="1">
+      <c r="C6" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="12">
         <v>1.9E-2</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="12">
         <v>0.02</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="12">
         <v>0.01</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="A7" s="8">
         <v>39629</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="8">
         <v>39688</v>
       </c>
-      <c r="C7" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="C7" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="12">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="12">
         <v>1.9E-2</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="A8" s="8">
         <v>39629</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="8">
         <v>39717</v>
       </c>
-      <c r="C8" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="1">
+      <c r="C8" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="12">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="12">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="12">
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="A9" s="8">
         <v>39721</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="8">
         <v>39751</v>
       </c>
-      <c r="C9" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="1">
+      <c r="C9" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="12">
         <v>-3.0000000000000001E-3</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="12">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="12">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="A10" s="8">
         <v>39721</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="8">
         <v>39777</v>
       </c>
-      <c r="C10" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="1">
+      <c r="C10" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="12">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="12">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="12">
         <v>-3.0000000000000001E-3</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="A11" s="8">
         <v>39721</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="8">
         <v>39805</v>
       </c>
-      <c r="C11" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="1">
+      <c r="C11" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="12">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="12">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="12">
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="A12" s="8">
         <v>39813</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="8">
         <v>39843</v>
       </c>
-      <c r="C12" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="1">
+      <c r="C12" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="12">
         <v>-3.7999999999999999E-2</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="12">
         <v>-5.3999999999999999E-2</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" s="12">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+      <c r="A13" s="8">
         <v>39813</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="8">
         <v>39871</v>
       </c>
-      <c r="C13" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="1">
+      <c r="C13" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="12">
         <v>-6.2E-2</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="12">
         <v>-5.3999999999999999E-2</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="12">
         <v>-3.7999999999999999E-2</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="A14" s="8">
         <v>39813</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="8">
         <v>39898</v>
       </c>
-      <c r="C14" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="1">
+      <c r="C14" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="12">
         <v>-6.3E-2</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="12">
         <v>-6.6000000000000003E-2</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="12">
         <v>-6.2E-2</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+      <c r="A15" s="8">
         <v>39903</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="8">
         <v>39932</v>
       </c>
-      <c r="C15" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="1">
+      <c r="C15" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="12">
         <v>-6.0999999999999999E-2</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="12">
         <v>-4.9000000000000002E-2</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="12">
         <v>-6.3E-2</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="A16" s="8">
         <v>39903</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="8">
         <v>39962</v>
       </c>
-      <c r="C16" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="1">
+      <c r="C16" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="12">
         <v>-5.7000000000000002E-2</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="12">
         <v>-5.5E-2</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" s="12">
         <v>-6.0999999999999999E-2</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="A17" s="8">
         <v>39903</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="8">
         <v>39989</v>
       </c>
-      <c r="C17" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="1">
+      <c r="C17" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="12">
         <v>-5.5E-2</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="12">
         <v>-5.7000000000000002E-2</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" s="12">
         <v>-5.7000000000000002E-2</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="A18" s="8">
         <v>39994</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="8">
         <v>40025</v>
       </c>
-      <c r="C18" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="1">
+      <c r="C18" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="12">
         <v>-0.01</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="12">
         <v>-1.2999999999999999E-2</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" s="12">
         <v>-6.4000000000000001E-2</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H18" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="A19" s="8">
         <v>39994</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="8">
         <v>40052</v>
       </c>
-      <c r="C19" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="1">
+      <c r="C19" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="12">
         <v>-0.01</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="12">
         <v>-1.2999999999999999E-2</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" s="12">
         <v>-0.01</v>
       </c>
-      <c r="H19" s="4">
+      <c r="H19" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="A20" s="8">
         <v>39994</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="8">
         <v>40086</v>
       </c>
-      <c r="C20" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="1">
+      <c r="C20" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="12">
         <v>-7.0000000000000001E-3</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="12">
         <v>-1.2E-2</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" s="12">
         <v>-0.01</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="A21" s="8">
         <v>40086</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="8">
         <v>40115</v>
       </c>
-      <c r="C21" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="1">
+      <c r="C21" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="12">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21" s="12">
         <v>3.1E-2</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" s="12">
         <v>-7.0000000000000001E-3</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H21" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="A22" s="8">
         <v>40086</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="8">
         <v>40141</v>
       </c>
-      <c r="C22" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="1">
+      <c r="C22" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="12">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="12">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22" s="12">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="H22" s="4">
+      <c r="H22" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="A23" s="8">
         <v>40086</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="8">
         <v>40169</v>
       </c>
-      <c r="C23" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="1">
+      <c r="C23" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="12">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="12">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G23" s="12">
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+      <c r="A24" s="8">
         <v>40178</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="8">
         <v>40207</v>
       </c>
-      <c r="C24" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="1">
+      <c r="C24" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="12">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="12">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G24" s="12">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="H24" s="4">
+      <c r="H24" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+      <c r="A25" s="8">
         <v>40178</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="8">
         <v>40235</v>
       </c>
-      <c r="C25" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="1">
+      <c r="C25" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="12">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="12">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G25" s="12">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="H25" s="4">
+      <c r="H25" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+      <c r="A26" s="8">
         <v>40178</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="8">
         <v>40263</v>
       </c>
-      <c r="C26" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="1">
+      <c r="C26" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="12">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26" s="12">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G26" s="12">
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+      <c r="A27" s="8">
         <v>40268</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="8">
         <v>40298</v>
       </c>
-      <c r="C27" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="1">
+      <c r="C27" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="12">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="12">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G27" s="12">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="H27" s="4">
+      <c r="H27" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+      <c r="A28" s="8">
         <v>40268</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="8">
         <v>40325</v>
       </c>
-      <c r="C28" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="1">
+      <c r="C28" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="12">
         <v>0.03</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28" s="12">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="G28" s="1">
+      <c r="G28" s="12">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="H28" s="4">
+      <c r="H28" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+      <c r="A29" s="8">
         <v>40268</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="8">
         <v>40354</v>
       </c>
-      <c r="C29" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="1">
+      <c r="C29" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="12">
         <v>2.7E-2</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29" s="12">
         <v>0.03</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G29" s="12">
         <v>0.03</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+      <c r="A30" s="8">
         <v>40359</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30" s="8">
         <v>40389</v>
       </c>
-      <c r="C30" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="1">
+      <c r="C30" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="12">
         <v>2.4E-2</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G30" s="12">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="H30" s="4">
+      <c r="H30" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+      <c r="A31" s="8">
         <v>40359</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="8">
         <v>40417</v>
       </c>
-      <c r="C31" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" s="1">
+      <c r="C31" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" s="12">
         <v>1.6E-2</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="12">
         <v>1.4E-2</v>
       </c>
-      <c r="G31" s="1">
+      <c r="G31" s="12">
         <v>2.4E-2</v>
       </c>
-      <c r="H31" s="4">
+      <c r="H31" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+      <c r="A32" s="8">
         <v>40359</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="8">
         <v>40451</v>
       </c>
-      <c r="C32" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="1">
+      <c r="C32" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="12">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="12">
         <v>1.6E-2</v>
       </c>
-      <c r="G32" s="1">
+      <c r="G32" s="12">
         <v>1.6E-2</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+      <c r="A33" s="8">
         <v>40451</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="8">
         <v>40480</v>
       </c>
-      <c r="C33" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" s="1">
+      <c r="C33" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="12">
         <v>0.02</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="12">
         <v>0.02</v>
       </c>
-      <c r="G33" s="1">
+      <c r="G33" s="12">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="H33" s="4">
+      <c r="H33" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+      <c r="A34" s="8">
         <v>40451</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="8">
         <v>40505</v>
       </c>
-      <c r="C34" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" s="1">
+      <c r="C34" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34" s="12">
         <v>2.4E-2</v>
       </c>
-      <c r="G34" s="1">
+      <c r="G34" s="12">
         <v>0.02</v>
       </c>
-      <c r="H34" s="4">
+      <c r="H34" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+      <c r="A35" s="8">
         <v>40451</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="8">
         <v>40534</v>
       </c>
-      <c r="C35" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E35" s="1">
+      <c r="C35" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35" s="12">
         <v>2.7E-2</v>
       </c>
-      <c r="G35" s="1">
+      <c r="G35" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
+      <c r="A36" s="8">
         <v>40543</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="8">
         <v>40571</v>
       </c>
-      <c r="C36" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E36" s="1">
+      <c r="C36" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="12">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36" s="12">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="G36" s="1">
+      <c r="G36" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="H36" s="4">
+      <c r="H36" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+      <c r="A37" s="8">
         <v>40543</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="8">
         <v>40599</v>
       </c>
-      <c r="C37" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" s="1">
+      <c r="C37" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="12">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37" s="12">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="G37" s="1">
+      <c r="G37" s="12">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="H37" s="4">
+      <c r="H37" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
+      <c r="A38" s="8">
         <v>40543</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="8">
         <v>40627</v>
       </c>
-      <c r="C38" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="1">
+      <c r="C38" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="12">
         <v>3.1E-2</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38" s="12">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="G38" s="1">
+      <c r="G38" s="12">
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
+      <c r="A39" s="8">
         <v>40633</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="8">
         <v>40661</v>
       </c>
-      <c r="C39" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" s="1">
+      <c r="C39" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="12">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="12">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="G39" s="1">
+      <c r="G39" s="12">
         <v>3.1E-2</v>
       </c>
-      <c r="H39" s="4">
+      <c r="H39" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+      <c r="A40" s="8">
         <v>40633</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40" s="8">
         <v>40689</v>
       </c>
-      <c r="C40" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" s="1">
+      <c r="C40" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="12">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40" s="12">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="G40" s="1">
+      <c r="G40" s="12">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="H40" s="4">
+      <c r="H40" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+      <c r="A41" s="8">
         <v>40633</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="8">
         <v>40718</v>
       </c>
-      <c r="C41" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="1">
+      <c r="C41" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" s="12">
         <v>1.9E-2</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41" s="12">
         <v>1.9E-2</v>
       </c>
-      <c r="G41" s="1">
+      <c r="G41" s="12">
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+      <c r="A42" s="8">
         <v>40724</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42" s="8">
         <v>40753</v>
       </c>
-      <c r="C42" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="1">
+      <c r="C42" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="12">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F42" s="12">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="G42" s="1">
+      <c r="G42" s="12">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="H42" s="4">
+      <c r="H42" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+      <c r="A43" s="8">
         <v>40724</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="8">
         <v>40781</v>
       </c>
-      <c r="C43" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E43" s="1">
+      <c r="C43" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="12">
         <v>0.01</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F43" s="12">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="G43" s="1">
+      <c r="G43" s="12">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="H43" s="4">
+      <c r="H43" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+      <c r="A44" s="8">
         <v>40724</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="8">
         <v>40815</v>
       </c>
-      <c r="C44" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" s="1">
+      <c r="C44" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="12">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F44" s="12">
         <v>1.2E-2</v>
       </c>
-      <c r="G44" s="1">
+      <c r="G44" s="12">
         <v>0.01</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
+      <c r="A45" s="8">
         <v>40816</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="8">
         <v>40843</v>
       </c>
-      <c r="C45" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" s="1">
+      <c r="C45" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F45" s="12">
         <v>2.4E-2</v>
       </c>
-      <c r="G45" s="1">
+      <c r="G45" s="12">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="H45" s="4">
+      <c r="H45" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
+      <c r="A46" s="8">
         <v>40816</v>
       </c>
-      <c r="B46" s="2">
+      <c r="B46" s="8">
         <v>40869</v>
       </c>
-      <c r="C46" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E46" s="1">
+      <c r="C46" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="12">
         <v>0.02</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F46" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G46" s="1">
+      <c r="G46" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="H46" s="4">
+      <c r="H46" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
+      <c r="A47" s="8">
         <v>40816</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47" s="8">
         <v>40899</v>
       </c>
-      <c r="C47" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E47" s="1">
+      <c r="C47" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="12">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F47" s="12">
         <v>0.02</v>
       </c>
-      <c r="G47" s="1">
+      <c r="G47" s="12">
         <v>0.02</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
+      <c r="A48" s="8">
         <v>40908</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48" s="8">
         <v>40935</v>
       </c>
-      <c r="C48" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" s="1">
+      <c r="C48" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="12">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F48" s="12">
         <v>0.03</v>
       </c>
-      <c r="G48" s="1">
+      <c r="G48" s="12">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="H48" s="4">
+      <c r="H48" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
+      <c r="A49" s="8">
         <v>40908</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="8">
         <v>40968</v>
       </c>
-      <c r="C49" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E49" s="1">
+      <c r="C49" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="12">
         <v>0.03</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F49" s="12">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="G49" s="1">
+      <c r="G49" s="12">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="H49" s="4">
+      <c r="H49" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
+      <c r="A50" s="8">
         <v>40908</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50" s="8">
         <v>40997</v>
       </c>
-      <c r="C50" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="1">
+      <c r="C50" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="12">
         <v>0.03</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F50" s="12">
         <v>0.03</v>
       </c>
-      <c r="G50" s="1">
+      <c r="G50" s="12">
         <v>0.03</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
+      <c r="A51" s="8">
         <v>40999</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="8">
         <v>41026</v>
       </c>
-      <c r="C51" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E51" s="1">
+      <c r="C51" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="12">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="F51" s="1">
+      <c r="F51" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G51" s="1">
+      <c r="G51" s="12">
         <v>0.03</v>
       </c>
-      <c r="H51" s="4">
+      <c r="H51" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
+      <c r="A52" s="8">
         <v>40999</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52" s="8">
         <v>41060</v>
       </c>
-      <c r="C52" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" s="1">
+      <c r="C52" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="12">
         <v>1.9E-2</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F52" s="12">
         <v>1.9E-2</v>
       </c>
-      <c r="G52" s="1">
+      <c r="G52" s="12">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="H52" s="4">
+      <c r="H52" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
+      <c r="A53" s="8">
         <v>40999</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" s="8">
         <v>41088</v>
       </c>
-      <c r="C53" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E53" s="1">
+      <c r="C53" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" s="12">
         <v>1.9E-2</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F53" s="12">
         <v>1.9E-2</v>
       </c>
-      <c r="G53" s="1">
+      <c r="G53" s="12">
         <v>1.9E-2</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
+      <c r="A54" s="8">
         <v>41090</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54" s="8">
         <v>41117</v>
       </c>
-      <c r="C54" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E54" s="1">
+      <c r="C54" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" s="12">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="F54" s="1">
+      <c r="F54" s="12">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="G54" s="1">
+      <c r="G54" s="12">
         <v>0.02</v>
       </c>
-      <c r="H54" s="4">
+      <c r="H54" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
+      <c r="A55" s="8">
         <v>41090</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55" s="8">
         <v>41150</v>
       </c>
-      <c r="C55" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E55" s="1">
+      <c r="C55" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" s="12">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F55" s="12">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="G55" s="1">
+      <c r="G55" s="12">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="H55" s="4">
+      <c r="H55" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
+      <c r="A56" s="8">
         <v>41090</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="8">
         <v>41179</v>
       </c>
-      <c r="C56" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E56" s="1">
+      <c r="C56" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="12">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F56" s="12">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="G56" s="1">
+      <c r="G56" s="12">
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
+      <c r="A57" s="8">
         <v>41182</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57" s="8">
         <v>41208</v>
       </c>
-      <c r="C57" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E57" s="1">
+      <c r="C57" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" s="12">
         <v>0.02</v>
       </c>
-      <c r="F57" s="1">
+      <c r="F57" s="12">
         <v>1.9E-2</v>
       </c>
-      <c r="G57" s="1">
+      <c r="G57" s="12">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="H57" s="4">
+      <c r="H57" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
+      <c r="A58" s="8">
         <v>41182</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B58" s="8">
         <v>41242</v>
       </c>
-      <c r="C58" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E58" s="1">
+      <c r="C58" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" s="12">
         <v>2.7E-2</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F58" s="12">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="G58" s="1">
+      <c r="G58" s="12">
         <v>0.02</v>
       </c>
-      <c r="H58" s="4">
+      <c r="H58" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
+      <c r="A59" s="8">
         <v>41182</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59" s="8">
         <v>41263</v>
       </c>
-      <c r="C59" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E59" s="1">
+      <c r="C59" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" s="12">
         <v>3.1E-2</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F59" s="12">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="G59" s="1">
+      <c r="G59" s="12">
         <v>2.7E-2</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
+      <c r="A60" s="8">
         <v>41274</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60" s="8">
         <v>41304</v>
       </c>
-      <c r="C60" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E60" s="1">
+      <c r="C60" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" s="12">
         <v>-1E-3</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F60" s="12">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="G60" s="1">
+      <c r="G60" s="12">
         <v>3.1E-2</v>
       </c>
-      <c r="H60" s="4">
+      <c r="H60" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
+      <c r="A61" s="8">
         <v>41274</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61" s="8">
         <v>41333</v>
       </c>
-      <c r="C61" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E61" s="1">
+      <c r="C61" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" s="12">
         <v>1E-3</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F61" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G61" s="1">
+      <c r="G61" s="12">
         <v>-1E-3</v>
       </c>
-      <c r="H61" s="4">
+      <c r="H61" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
+      <c r="A62" s="8">
         <v>41274</v>
       </c>
-      <c r="B62" s="2">
+      <c r="B62" s="8">
         <v>41361</v>
       </c>
-      <c r="C62" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E62" s="1">
+      <c r="C62" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" s="12">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F62" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G62" s="1">
+      <c r="G62" s="12">
         <v>1E-3</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
+      <c r="A63" s="8">
         <v>41364</v>
       </c>
-      <c r="B63" s="2">
+      <c r="B63" s="8">
         <v>41390</v>
       </c>
-      <c r="C63" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E63" s="1">
+      <c r="C63" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F63" s="1">
+      <c r="F63" s="12">
         <v>0.03</v>
       </c>
-      <c r="G63" s="1">
+      <c r="G63" s="12">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="H63" s="4">
+      <c r="H63" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
+      <c r="A64" s="8">
         <v>41364</v>
       </c>
-      <c r="B64" s="2">
+      <c r="B64" s="8">
         <v>41424</v>
       </c>
-      <c r="C64" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E64" s="1">
+      <c r="C64" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" s="12">
         <v>2.4E-2</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F64" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G64" s="1">
+      <c r="G64" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="H64" s="4">
+      <c r="H64" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
+      <c r="A65" s="8">
         <v>41364</v>
       </c>
-      <c r="B65" s="2">
+      <c r="B65" s="8">
         <v>41451</v>
       </c>
-      <c r="C65" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E65" s="1">
+      <c r="C65" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" s="12">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="F65" s="1">
+      <c r="F65" s="12">
         <v>2.4E-2</v>
       </c>
-      <c r="G65" s="1">
+      <c r="G65" s="12">
         <v>2.4E-2</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
+      <c r="A66" s="8">
         <v>41455</v>
       </c>
-      <c r="B66" s="2">
+      <c r="B66" s="8">
         <v>41486</v>
       </c>
-      <c r="C66" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E66" s="1">
+      <c r="C66" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" s="12">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="F66" s="1">
+      <c r="F66" s="12">
         <v>0.01</v>
       </c>
-      <c r="G66" s="1">
+      <c r="G66" s="12">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="H66" s="4">
+      <c r="H66" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
+      <c r="A67" s="8">
         <v>41455</v>
       </c>
-      <c r="B67" s="2">
+      <c r="B67" s="8">
         <v>41515</v>
       </c>
-      <c r="C67" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E67" s="1">
+      <c r="C67" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F67" s="12">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="G67" s="1">
+      <c r="G67" s="12">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="H67" s="4">
+      <c r="H67" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
+      <c r="A68" s="8">
         <v>41455</v>
       </c>
-      <c r="B68" s="2">
+      <c r="B68" s="8">
         <v>41543</v>
       </c>
-      <c r="C68" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E68" s="1">
+      <c r="C68" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F68" s="1">
+      <c r="F68" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="G68" s="1">
+      <c r="G68" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
+      <c r="A69" s="8">
         <v>41547</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B69" s="8">
         <v>41585</v>
       </c>
-      <c r="C69" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E69" s="1">
+      <c r="C69" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E69" s="12">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F69" s="12">
         <v>0.02</v>
       </c>
-      <c r="G69" s="1">
+      <c r="G69" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="H69" s="4">
+      <c r="H69" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
+      <c r="A70" s="8">
         <v>41547</v>
       </c>
-      <c r="B70" s="2">
+      <c r="B70" s="8">
         <v>41613</v>
       </c>
-      <c r="C70" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E70" s="1">
+      <c r="C70" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E70" s="12">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F70" s="12">
         <v>0.03</v>
       </c>
-      <c r="G70" s="1">
+      <c r="G70" s="12">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="H70" s="4">
+      <c r="H70" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
+      <c r="A71" s="8">
         <v>41547</v>
       </c>
-      <c r="B71" s="2">
+      <c r="B71" s="8">
         <v>41628</v>
       </c>
-      <c r="C71" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E71" s="1">
+      <c r="C71" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E71" s="12">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F71" s="12">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="G71" s="1">
+      <c r="G71" s="12">
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
+      <c r="A72" s="8">
         <v>41639</v>
       </c>
-      <c r="B72" s="2">
+      <c r="B72" s="8">
         <v>41669</v>
       </c>
-      <c r="C72" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E72" s="1">
+      <c r="C72" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="12">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="F72" s="1">
+      <c r="F72" s="12">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="G72" s="1">
+      <c r="G72" s="12">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="H72" s="4">
+      <c r="H72" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
+      <c r="A73" s="8">
         <v>41639</v>
       </c>
-      <c r="B73" s="2">
+      <c r="B73" s="8">
         <v>41698</v>
       </c>
-      <c r="C73" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E73" s="1">
+      <c r="C73" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E73" s="12">
         <v>2.4E-2</v>
       </c>
-      <c r="F73" s="1">
+      <c r="F73" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G73" s="1">
+      <c r="G73" s="12">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="H73" s="4">
+      <c r="H73" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
+      <c r="A74" s="8">
         <v>41639</v>
       </c>
-      <c r="B74" s="2">
+      <c r="B74" s="8">
         <v>41725</v>
       </c>
-      <c r="C74" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E74" s="1">
+      <c r="C74" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="F74" s="1">
+      <c r="F74" s="12">
         <v>2.7E-2</v>
       </c>
-      <c r="G74" s="1">
+      <c r="G74" s="12">
         <v>2.4E-2</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
+      <c r="A75" s="8">
         <v>41729</v>
       </c>
-      <c r="B75" s="2">
+      <c r="B75" s="8">
         <v>41759</v>
       </c>
-      <c r="C75" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E75" s="1">
+      <c r="C75" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" s="12">
         <v>1E-3</v>
       </c>
-      <c r="F75" s="1">
+      <c r="F75" s="12">
         <v>1.2E-2</v>
       </c>
-      <c r="G75" s="1">
+      <c r="G75" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="H75" s="4">
+      <c r="H75" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
+      <c r="A76" s="8">
         <v>41729</v>
       </c>
-      <c r="B76" s="2">
+      <c r="B76" s="8">
         <v>41788</v>
       </c>
-      <c r="C76" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E76" s="1">
+      <c r="C76" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" s="12">
         <v>-0.01</v>
       </c>
-      <c r="F76" s="1">
+      <c r="F76" s="12">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="G76" s="1">
+      <c r="G76" s="12">
         <v>1E-3</v>
       </c>
-      <c r="H76" s="4">
+      <c r="H76" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
+      <c r="A77" s="8">
         <v>41729</v>
       </c>
-      <c r="B77" s="2">
+      <c r="B77" s="8">
         <v>41815</v>
       </c>
-      <c r="C77" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E77" s="1">
+      <c r="C77" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" s="12">
         <v>-2.9000000000000001E-2</v>
       </c>
-      <c r="F77" s="1">
+      <c r="F77" s="12">
         <v>-1.7000000000000001E-2</v>
       </c>
-      <c r="G77" s="1">
+      <c r="G77" s="12">
         <v>-0.01</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
+      <c r="A78" s="8">
         <v>41820</v>
       </c>
-      <c r="B78" s="2">
+      <c r="B78" s="8">
         <v>41850</v>
       </c>
-      <c r="C78" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E78" s="1">
+      <c r="C78" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" s="12">
         <v>0.04</v>
       </c>
-      <c r="F78" s="1">
+      <c r="F78" s="12">
         <v>0.03</v>
       </c>
-      <c r="G78" s="1">
+      <c r="G78" s="12">
         <v>-2.1000000000000001E-2</v>
       </c>
-      <c r="H78" s="4">
+      <c r="H78" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
+      <c r="A79" s="8">
         <v>41820</v>
       </c>
-      <c r="B79" s="2">
+      <c r="B79" s="8">
         <v>41879</v>
       </c>
-      <c r="C79" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E79" s="1">
+      <c r="C79" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" s="12">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="F79" s="1">
+      <c r="F79" s="12">
         <v>3.9E-2</v>
       </c>
-      <c r="G79" s="1">
+      <c r="G79" s="12">
         <v>0.04</v>
       </c>
-      <c r="H79" s="4">
+      <c r="H79" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
+      <c r="A80" s="8">
         <v>41820</v>
       </c>
-      <c r="B80" s="2">
+      <c r="B80" s="8">
         <v>41908</v>
       </c>
-      <c r="C80" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E80" s="1">
+      <c r="C80" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" s="12">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="F80" s="1">
+      <c r="F80" s="12">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="G80" s="1">
+      <c r="G80" s="12">
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="2">
+      <c r="A81" s="8">
         <v>41912</v>
       </c>
-      <c r="B81" s="2">
+      <c r="B81" s="8">
         <v>41942</v>
       </c>
-      <c r="C81" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E81" s="1">
+      <c r="C81" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" s="12">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="F81" s="1">
+      <c r="F81" s="12">
         <v>0.03</v>
       </c>
-      <c r="G81" s="1">
+      <c r="G81" s="12">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="H81" s="4">
+      <c r="H81" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="2">
+      <c r="A82" s="8">
         <v>41912</v>
       </c>
-      <c r="B82" s="2">
+      <c r="B82" s="8">
         <v>41968</v>
       </c>
-      <c r="C82" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E82" s="1">
+      <c r="C82" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E82" s="12">
         <v>3.9E-2</v>
       </c>
-      <c r="F82" s="1">
+      <c r="F82" s="12">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="G82" s="1">
+      <c r="G82" s="12">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="H82" s="4">
+      <c r="H82" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
+      <c r="A83" s="8">
         <v>41912</v>
       </c>
-      <c r="B83" s="2">
+      <c r="B83" s="8">
         <v>41996</v>
       </c>
-      <c r="C83" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E83" s="1">
+      <c r="C83" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83" s="12">
         <v>0.05</v>
       </c>
-      <c r="F83" s="1">
+      <c r="F83" s="12">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="G83" s="1">
+      <c r="G83" s="12">
         <v>3.9E-2</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
+      <c r="A84" s="8">
         <v>42004</v>
       </c>
-      <c r="B84" s="2">
+      <c r="B84" s="8">
         <v>42034</v>
       </c>
-      <c r="C84" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E84" s="1">
+      <c r="C84" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E84" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="F84" s="1">
+      <c r="F84" s="12">
         <v>0.03</v>
       </c>
-      <c r="G84" s="1">
+      <c r="G84" s="12">
         <v>0.05</v>
       </c>
-      <c r="H84" s="4">
+      <c r="H84" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
+      <c r="A85" s="8">
         <v>42004</v>
       </c>
-      <c r="B85" s="2">
+      <c r="B85" s="8">
         <v>42062</v>
       </c>
-      <c r="C85" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E85" s="1">
+      <c r="C85" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E85" s="12">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="F85" s="1">
+      <c r="F85" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="G85" s="1">
+      <c r="G85" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="H85" s="4">
+      <c r="H85" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="2">
+      <c r="A86" s="8">
         <v>42004</v>
       </c>
-      <c r="B86" s="2">
+      <c r="B86" s="8">
         <v>42090</v>
       </c>
-      <c r="C86" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E86" s="1">
+      <c r="C86" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" s="12">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="F86" s="1">
+      <c r="F86" s="12">
         <v>2.4E-2</v>
       </c>
-      <c r="G86" s="1">
+      <c r="G86" s="12">
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="2">
+      <c r="A87" s="8">
         <v>42094</v>
       </c>
-      <c r="B87" s="2">
+      <c r="B87" s="8">
         <v>42123</v>
       </c>
-      <c r="C87" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E87" s="1">
+      <c r="C87" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" s="12">
         <v>2E-3</v>
       </c>
-      <c r="F87" s="1">
+      <c r="F87" s="12">
         <v>0.01</v>
       </c>
-      <c r="G87" s="1">
+      <c r="G87" s="12">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="H87" s="4">
+      <c r="H87" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="2">
+      <c r="A88" s="8">
         <v>42094</v>
       </c>
-      <c r="B88" s="2">
+      <c r="B88" s="8">
         <v>42153</v>
       </c>
-      <c r="C88" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E88" s="1">
+      <c r="C88" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E88" s="12">
         <v>-7.0000000000000001E-3</v>
       </c>
-      <c r="F88" s="1">
+      <c r="F88" s="12">
         <v>-8.0000000000000002E-3</v>
       </c>
-      <c r="G88" s="1">
+      <c r="G88" s="12">
         <v>2E-3</v>
       </c>
-      <c r="H88" s="4">
+      <c r="H88" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="2">
+      <c r="A89" s="8">
         <v>42094</v>
       </c>
-      <c r="B89" s="2">
+      <c r="B89" s="8">
         <v>42179</v>
       </c>
-      <c r="C89" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E89" s="1">
+      <c r="C89" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E89" s="12">
         <v>-2E-3</v>
       </c>
-      <c r="F89" s="1">
+      <c r="F89" s="12">
         <v>-2E-3</v>
       </c>
-      <c r="G89" s="1">
+      <c r="G89" s="12">
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="2">
+      <c r="A90" s="8">
         <v>42185</v>
       </c>
-      <c r="B90" s="2">
+      <c r="B90" s="8">
         <v>42215</v>
       </c>
-      <c r="C90" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E90" s="1">
+      <c r="C90" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E90" s="12">
         <v>2.3E-2</v>
       </c>
-      <c r="F90" s="1">
+      <c r="F90" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="G90" s="1">
+      <c r="G90" s="12">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="H90" s="4">
+      <c r="H90" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="2">
+      <c r="A91" s="8">
         <v>42185</v>
       </c>
-      <c r="B91" s="2">
+      <c r="B91" s="8">
         <v>42243</v>
       </c>
-      <c r="C91" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D91" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E91" s="1">
+      <c r="C91" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" s="12">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="F91" s="1">
+      <c r="F91" s="12">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="G91" s="1">
+      <c r="G91" s="12">
         <v>2.3E-2</v>
       </c>
-      <c r="H91" s="4">
+      <c r="H91" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="2">
+      <c r="A92" s="8">
         <v>42185</v>
       </c>
-      <c r="B92" s="2">
+      <c r="B92" s="8">
         <v>42272</v>
       </c>
-      <c r="C92" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D92" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E92" s="1">
+      <c r="C92" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E92" s="12">
         <v>3.9E-2</v>
       </c>
-      <c r="F92" s="1">
+      <c r="F92" s="12">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="G92" s="1">
+      <c r="G92" s="12">
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
+      <c r="A93" s="8">
         <v>42277</v>
       </c>
-      <c r="B93" s="2">
+      <c r="B93" s="8">
         <v>42306</v>
       </c>
-      <c r="C93" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D93" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E93" s="1">
+      <c r="C93" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E93" s="12">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="F93" s="1">
+      <c r="F93" s="12">
         <v>1.6E-2</v>
       </c>
-      <c r="G93" s="1">
+      <c r="G93" s="12">
         <v>3.9E-2</v>
       </c>
-      <c r="H93" s="4">
+      <c r="H93" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
+      <c r="A94" s="8">
         <v>42277</v>
       </c>
-      <c r="B94" s="2">
+      <c r="B94" s="8">
         <v>42332</v>
       </c>
-      <c r="C94" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E94" s="1">
+      <c r="C94" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="F94" s="1">
+      <c r="F94" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="G94" s="1">
+      <c r="G94" s="12">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="H94" s="4">
+      <c r="H94" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="2">
+      <c r="A95" s="8">
         <v>42277</v>
       </c>
-      <c r="B95" s="2">
+      <c r="B95" s="8">
         <v>42360</v>
       </c>
-      <c r="C95" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E95" s="1">
+      <c r="C95" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E95" s="12">
         <v>0.02</v>
       </c>
-      <c r="F95" s="1">
+      <c r="F95" s="12">
         <v>1.9E-2</v>
       </c>
-      <c r="G95" s="1">
+      <c r="G95" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
+      <c r="A96" s="8">
         <v>42369</v>
       </c>
-      <c r="B96" s="2">
+      <c r="B96" s="8">
         <v>42398</v>
       </c>
-      <c r="C96" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D96" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E96" s="1">
+      <c r="C96" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="12">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="F96" s="1">
+      <c r="F96" s="12">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="G96" s="1">
+      <c r="G96" s="12">
         <v>0.02</v>
       </c>
-      <c r="H96" s="4">
+      <c r="H96" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="2">
+      <c r="A97" s="8">
         <v>42369</v>
       </c>
-      <c r="B97" s="2">
+      <c r="B97" s="8">
         <v>42426</v>
       </c>
-      <c r="C97" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E97" s="1">
+      <c r="C97" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E97" s="12">
         <v>0.01</v>
       </c>
-      <c r="F97" s="1">
+      <c r="F97" s="12">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="G97" s="1">
+      <c r="G97" s="12">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="H97" s="4">
+      <c r="H97" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="2">
+      <c r="A98" s="8">
         <v>42369</v>
       </c>
-      <c r="B98" s="2">
+      <c r="B98" s="8">
         <v>42454</v>
       </c>
-      <c r="C98" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E98" s="1">
+      <c r="C98" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E98" s="12">
         <v>1.4E-2</v>
       </c>
-      <c r="F98" s="1">
+      <c r="F98" s="12">
         <v>0.01</v>
       </c>
-      <c r="G98" s="1">
+      <c r="G98" s="12">
         <v>0.01</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="2">
+      <c r="A99" s="8">
         <v>42460</v>
       </c>
-      <c r="B99" s="2">
+      <c r="B99" s="8">
         <v>42488</v>
       </c>
-      <c r="C99" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D99" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E99" s="1">
+      <c r="C99" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F99" s="1">
+      <c r="F99" s="12">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="G99" s="1">
+      <c r="G99" s="12">
         <v>1.4E-2</v>
       </c>
-      <c r="H99" s="4">
+      <c r="H99" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="2">
+      <c r="A100" s="8">
         <v>42460</v>
       </c>
-      <c r="B100" s="2">
+      <c r="B100" s="8">
         <v>42517</v>
       </c>
-      <c r="C100" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D100" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E100" s="1">
+      <c r="C100" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" s="12">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="F100" s="1">
+      <c r="F100" s="12">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="G100" s="1">
+      <c r="G100" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="H100" s="4">
+      <c r="H100" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="2">
+      <c r="A101" s="8">
         <v>42460</v>
       </c>
-      <c r="B101" s="2">
+      <c r="B101" s="8">
         <v>42549</v>
       </c>
-      <c r="C101" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E101" s="1">
+      <c r="C101" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E101" s="12">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="F101" s="1">
+      <c r="F101" s="12">
         <v>0.01</v>
       </c>
-      <c r="G101" s="1">
+      <c r="G101" s="12">
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="2">
+      <c r="A102" s="8">
         <v>42551</v>
       </c>
-      <c r="B102" s="2">
+      <c r="B102" s="8">
         <v>42580</v>
       </c>
-      <c r="C102" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D102" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E102" s="1">
+      <c r="C102" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E102" s="12">
         <v>1.2E-2</v>
       </c>
-      <c r="F102" s="1">
+      <c r="F102" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="G102" s="1">
+      <c r="G102" s="12">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="H102" s="4">
+      <c r="H102" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="2">
+      <c r="A103" s="8">
         <v>42551</v>
       </c>
-      <c r="B103" s="2">
+      <c r="B103" s="8">
         <v>42608</v>
       </c>
-      <c r="C103" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E103" s="1">
+      <c r="C103" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" s="12">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="F103" s="1">
+      <c r="F103" s="12">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="G103" s="1">
+      <c r="G103" s="12">
         <v>1.2E-2</v>
       </c>
-      <c r="H103" s="4">
+      <c r="H103" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="2">
+      <c r="A104" s="8">
         <v>42551</v>
       </c>
-      <c r="B104" s="2">
+      <c r="B104" s="8">
         <v>42642</v>
       </c>
-      <c r="C104" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E104" s="1">
+      <c r="C104" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" s="12">
         <v>1.4E-2</v>
       </c>
-      <c r="F104" s="1">
+      <c r="F104" s="12">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="G104" s="1">
+      <c r="G104" s="12">
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="2">
+      <c r="A105" s="8">
         <v>42643</v>
       </c>
-      <c r="B105" s="2">
+      <c r="B105" s="8">
         <v>42671</v>
       </c>
-      <c r="C105" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E105" s="1">
+      <c r="C105" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E105" s="12">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="F105" s="1">
+      <c r="F105" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G105" s="1">
+      <c r="G105" s="12">
         <v>1.4E-2</v>
       </c>
-      <c r="H105" s="4">
+      <c r="H105" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="2">
+      <c r="A106" s="8">
         <v>42643</v>
       </c>
-      <c r="B106" s="2">
+      <c r="B106" s="8">
         <v>42703</v>
       </c>
-      <c r="C106" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D106" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E106" s="1">
+      <c r="C106" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E106" s="12">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="F106" s="1">
+      <c r="F106" s="12">
         <v>0.03</v>
       </c>
-      <c r="G106" s="1">
+      <c r="G106" s="12">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="H106" s="4">
+      <c r="H106" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="2">
+      <c r="A107" s="8">
         <v>42643</v>
       </c>
-      <c r="B107" s="2">
+      <c r="B107" s="8">
         <v>42726</v>
       </c>
-      <c r="C107" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D107" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E107" s="1">
+      <c r="C107" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E107" s="12">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="F107" s="1">
+      <c r="F107" s="12">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="G107" s="1">
+      <c r="G107" s="12">
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="2">
+      <c r="A108" s="8">
         <v>42735</v>
       </c>
-      <c r="B108" s="2">
+      <c r="B108" s="8">
         <v>42762</v>
       </c>
-      <c r="C108" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D108" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E108" s="1">
+      <c r="C108" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E108" s="12">
         <v>1.9E-2</v>
       </c>
-      <c r="F108" s="1">
+      <c r="F108" s="12">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="G108" s="1">
+      <c r="G108" s="12">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="H108" s="4">
+      <c r="H108" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="2">
+      <c r="A109" s="8">
         <v>42735</v>
       </c>
-      <c r="B109" s="2">
+      <c r="B109" s="8">
         <v>42794</v>
       </c>
-      <c r="C109" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D109" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E109" s="1">
+      <c r="C109" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E109" s="12">
         <v>1.9E-2</v>
       </c>
-      <c r="F109" s="1">
+      <c r="F109" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="G109" s="1">
+      <c r="G109" s="12">
         <v>1.9E-2</v>
       </c>
-      <c r="H109" s="4">
+      <c r="H109" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="2">
+      <c r="A110" s="8">
         <v>42735</v>
       </c>
-      <c r="B110" s="2">
+      <c r="B110" s="8">
         <v>42824</v>
       </c>
-      <c r="C110" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D110" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E110" s="1">
+      <c r="C110" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E110" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="F110" s="1">
+      <c r="F110" s="12">
         <v>0.02</v>
       </c>
-      <c r="G110" s="1">
+      <c r="G110" s="12">
         <v>1.9E-2</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="2">
+      <c r="A111" s="8">
         <v>42825</v>
       </c>
-      <c r="B111" s="2">
+      <c r="B111" s="8">
         <v>42853</v>
       </c>
-      <c r="C111" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D111" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E111" s="1">
+      <c r="C111" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E111" s="12">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="F111" s="1">
+      <c r="F111" s="12">
         <v>1.2E-2</v>
       </c>
-      <c r="G111" s="1">
+      <c r="G111" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="H111" s="4">
+      <c r="H111" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="2">
+      <c r="A112" s="8">
         <v>42825</v>
       </c>
-      <c r="B112" s="2">
+      <c r="B112" s="8">
         <v>42881</v>
       </c>
-      <c r="C112" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D112" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E112" s="1">
+      <c r="C112" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" s="12">
         <v>1.2E-2</v>
       </c>
-      <c r="F112" s="1">
+      <c r="F112" s="12">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="G112" s="1">
+      <c r="G112" s="12">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="H112" s="4">
+      <c r="H112" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" s="2">
+      <c r="A113" s="8">
         <v>42825</v>
       </c>
-      <c r="B113" s="2">
+      <c r="B113" s="8">
         <v>42915</v>
       </c>
-      <c r="C113" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D113" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E113" s="1">
+      <c r="C113" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E113" s="12">
         <v>1.4E-2</v>
       </c>
-      <c r="F113" s="1">
+      <c r="F113" s="12">
         <v>1.2E-2</v>
       </c>
-      <c r="G113" s="1">
+      <c r="G113" s="12">
         <v>1.2E-2</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" s="2">
+      <c r="A114" s="8">
         <v>42916</v>
       </c>
-      <c r="B114" s="2">
+      <c r="B114" s="8">
         <v>42944</v>
       </c>
-      <c r="C114" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D114" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E114" s="1">
+      <c r="C114" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E114" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="F114" s="1">
+      <c r="F114" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="G114" s="1">
+      <c r="G114" s="12">
         <v>1.2E-2</v>
       </c>
-      <c r="H114" s="4">
+      <c r="H114" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="2">
+      <c r="A115" s="8">
         <v>42916</v>
       </c>
-      <c r="B115" s="2">
+      <c r="B115" s="8">
         <v>42977</v>
       </c>
-      <c r="C115" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D115" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E115" s="1">
+      <c r="C115" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E115" s="12">
         <v>0.03</v>
       </c>
-      <c r="F115" s="1">
+      <c r="F115" s="12">
         <v>2.7E-2</v>
       </c>
-      <c r="G115" s="1">
+      <c r="G115" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="H115" s="4">
+      <c r="H115" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="2">
+      <c r="A116" s="8">
         <v>42916</v>
       </c>
-      <c r="B116" s="2">
+      <c r="B116" s="8">
         <v>43006</v>
       </c>
-      <c r="C116" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D116" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E116" s="1">
+      <c r="C116" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E116" s="12">
         <v>3.1E-2</v>
       </c>
-      <c r="F116" s="1">
+      <c r="F116" s="12">
         <v>0.03</v>
       </c>
-      <c r="G116" s="1">
+      <c r="G116" s="12">
         <v>0.03</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" s="2">
+      <c r="A117" s="8">
         <v>43008</v>
       </c>
-      <c r="B117" s="2">
+      <c r="B117" s="8">
         <v>43035</v>
       </c>
-      <c r="C117" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D117" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E117" s="1">
+      <c r="C117" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E117" s="12">
         <v>0.03</v>
       </c>
-      <c r="F117" s="1">
+      <c r="F117" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G117" s="1">
+      <c r="G117" s="12">
         <v>3.1E-2</v>
       </c>
-      <c r="H117" s="4">
+      <c r="H117" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" s="2">
+      <c r="A118" s="8">
         <v>43008</v>
       </c>
-      <c r="B118" s="2">
+      <c r="B118" s="8">
         <v>43068</v>
       </c>
-      <c r="C118" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D118" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E118" s="1">
+      <c r="C118" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E118" s="12">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="F118" s="1">
+      <c r="F118" s="12">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="G118" s="1">
+      <c r="G118" s="12">
         <v>0.03</v>
       </c>
-      <c r="H118" s="4">
+      <c r="H118" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" s="2">
+      <c r="A119" s="8">
         <v>43008</v>
       </c>
-      <c r="B119" s="2">
+      <c r="B119" s="8">
         <v>43090</v>
       </c>
-      <c r="C119" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D119" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E119" s="1">
+      <c r="C119" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E119" s="12">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="F119" s="1">
+      <c r="F119" s="12">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="G119" s="1">
+      <c r="G119" s="12">
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="2">
+      <c r="A120" s="8">
         <v>43100</v>
       </c>
-      <c r="B120" s="2">
+      <c r="B120" s="8">
         <v>43126</v>
       </c>
-      <c r="C120" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D120" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E120" s="1">
+      <c r="C120" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E120" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="F120" s="1">
+      <c r="F120" s="12">
         <v>0.03</v>
       </c>
-      <c r="G120" s="1">
+      <c r="G120" s="12">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="H120" s="4">
+      <c r="H120" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" s="2">
+      <c r="A121" s="8">
         <v>43100</v>
       </c>
-      <c r="B121" s="2">
+      <c r="B121" s="8">
         <v>43159</v>
       </c>
-      <c r="C121" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D121" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E121" s="1">
+      <c r="C121" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E121" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F121" s="1">
+      <c r="F121" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G121" s="1">
+      <c r="G121" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="H121" s="4">
+      <c r="H121" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="2">
+      <c r="A122" s="8">
         <v>43100</v>
       </c>
-      <c r="B122" s="2">
+      <c r="B122" s="8">
         <v>43187</v>
       </c>
-      <c r="C122" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D122" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E122" s="1">
+      <c r="C122" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E122" s="12">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="F122" s="1">
+      <c r="F122" s="12">
         <v>2.7E-2</v>
       </c>
-      <c r="G122" s="1">
+      <c r="G122" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="2">
+      <c r="A123" s="8">
         <v>43190</v>
       </c>
-      <c r="B123" s="2">
+      <c r="B123" s="8">
         <v>43217</v>
       </c>
-      <c r="C123" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D123" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E123" s="1">
+      <c r="C123" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E123" s="12">
         <v>2.3E-2</v>
       </c>
-      <c r="F123" s="1">
+      <c r="F123" s="12">
         <v>0.02</v>
       </c>
-      <c r="G123" s="1">
+      <c r="G123" s="12">
         <v>2.3E-2</v>
       </c>
-      <c r="H123" s="4">
+      <c r="H123" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" s="2">
+      <c r="A124" s="8">
         <v>43190</v>
       </c>
-      <c r="B124" s="2">
+      <c r="B124" s="8">
         <v>43250</v>
       </c>
-      <c r="C124" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D124" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E124" s="1">
+      <c r="C124" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E124" s="12">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="F124" s="1">
+      <c r="F124" s="12">
         <v>2.3E-2</v>
       </c>
-      <c r="G124" s="1">
+      <c r="G124" s="12">
         <v>2.3E-2</v>
       </c>
-      <c r="H124" s="4">
+      <c r="H124" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="2">
+      <c r="A125" s="8">
         <v>43190</v>
       </c>
-      <c r="B125" s="2">
+      <c r="B125" s="8">
         <v>43279</v>
       </c>
-      <c r="C125" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D125" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E125" s="1">
+      <c r="C125" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E125" s="12">
         <v>0.02</v>
       </c>
-      <c r="F125" s="1">
+      <c r="F125" s="12">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="G125" s="1">
+      <c r="G125" s="12">
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="2">
+      <c r="A126" s="8">
         <v>43281</v>
       </c>
-      <c r="B126" s="2">
+      <c r="B126" s="8">
         <v>43308</v>
       </c>
-      <c r="C126" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D126" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E126" s="1">
+      <c r="C126" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E126" s="12">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="F126" s="1">
+      <c r="F126" s="12">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="G126" s="1">
+      <c r="G126" s="12">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="H126" s="4">
+      <c r="H126" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" s="2">
+      <c r="A127" s="8">
         <v>43281</v>
       </c>
-      <c r="B127" s="2">
+      <c r="B127" s="8">
         <v>43341</v>
       </c>
-      <c r="C127" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D127" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E127" s="1">
+      <c r="C127" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E127" s="12">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="F127" s="1">
+      <c r="F127" s="12">
         <v>0.04</v>
       </c>
-      <c r="G127" s="1">
+      <c r="G127" s="12">
         <v>0.02</v>
       </c>
-      <c r="H127" s="4">
+      <c r="H127" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" s="2">
+      <c r="A128" s="8">
         <v>43281</v>
       </c>
-      <c r="B128" s="2">
+      <c r="B128" s="8">
         <v>43370</v>
       </c>
-      <c r="C128" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D128" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E128" s="1">
+      <c r="C128" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E128" s="12">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="F128" s="1">
+      <c r="F128" s="12">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="G128" s="1">
+      <c r="G128" s="12">
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A129" s="2">
+      <c r="A129" s="8">
         <v>43373</v>
       </c>
-      <c r="B129" s="2">
+      <c r="B129" s="8">
         <v>43399</v>
       </c>
-      <c r="C129" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D129" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E129" s="1">
+      <c r="C129" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E129" s="12">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="F129" s="1">
+      <c r="F129" s="12">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="G129" s="1">
+      <c r="G129" s="12">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="H129" s="4">
+      <c r="H129" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A130" s="2">
+      <c r="A130" s="8">
         <v>43373</v>
       </c>
-      <c r="B130" s="2">
+      <c r="B130" s="8">
         <v>43432</v>
       </c>
-      <c r="C130" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D130" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E130" s="1">
+      <c r="C130" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E130" s="12">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="F130" s="1">
+      <c r="F130" s="12">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="G130" s="1">
+      <c r="G130" s="12">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="H130" s="4">
+      <c r="H130" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" s="2">
+      <c r="A131" s="8">
         <v>43373</v>
       </c>
-      <c r="B131" s="2">
+      <c r="B131" s="8">
         <v>43455</v>
       </c>
-      <c r="C131" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D131" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E131" s="1">
+      <c r="C131" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E131" s="12">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="F131" s="1">
+      <c r="F131" s="12">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="G131" s="1">
+      <c r="G131" s="12">
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A132" s="2">
+      <c r="A132" s="8">
         <v>43465</v>
       </c>
-      <c r="B132" s="2">
+      <c r="B132" s="8">
         <v>43524</v>
       </c>
-      <c r="C132" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D132" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E132" s="1">
+      <c r="C132" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E132" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="F132" s="1">
+      <c r="F132" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="G132" s="1">
+      <c r="G132" s="12">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="H132" s="4">
+      <c r="H132" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A133" s="2">
+      <c r="A133" s="8">
         <v>43465</v>
       </c>
-      <c r="B133" s="2">
+      <c r="B133" s="8">
         <v>43552</v>
       </c>
-      <c r="C133" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D133" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E133" s="1">
+      <c r="C133" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E133" s="12">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="F133" s="1">
+      <c r="F133" s="12">
         <v>2.4E-2</v>
       </c>
-      <c r="G133" s="1">
+      <c r="G133" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A134" s="2">
+      <c r="A134" s="8">
         <v>43555</v>
       </c>
-      <c r="B134" s="2">
+      <c r="B134" s="8">
         <v>43581</v>
       </c>
-      <c r="C134" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D134" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E134" s="1">
+      <c r="C134" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E134" s="12">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="F134" s="1">
+      <c r="F134" s="12">
         <v>0.02</v>
       </c>
-      <c r="G134" s="1">
+      <c r="G134" s="12">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="H134" s="4">
+      <c r="H134" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A135" s="2">
+      <c r="A135" s="8">
         <v>43555</v>
       </c>
-      <c r="B135" s="2">
+      <c r="B135" s="8">
         <v>43615</v>
       </c>
-      <c r="C135" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D135" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E135" s="1">
+      <c r="C135" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E135" s="12">
         <v>3.1E-2</v>
       </c>
-      <c r="F135" s="1">
+      <c r="F135" s="12">
         <v>3.1E-2</v>
       </c>
-      <c r="G135" s="1">
+      <c r="G135" s="12">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="H135" s="4">
+      <c r="H135" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A136" s="2">
+      <c r="A136" s="8">
         <v>43555</v>
       </c>
-      <c r="B136" s="2">
+      <c r="B136" s="8">
         <v>43643</v>
       </c>
-      <c r="C136" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D136" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E136" s="1">
+      <c r="C136" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E136" s="12">
         <v>3.1E-2</v>
       </c>
-      <c r="F136" s="1">
+      <c r="F136" s="12">
         <v>3.1E-2</v>
       </c>
-      <c r="G136" s="1">
+      <c r="G136" s="12">
         <v>3.1E-2</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A137" s="2">
+      <c r="A137" s="8">
         <v>43646</v>
       </c>
-      <c r="B137" s="2">
+      <c r="B137" s="8">
         <v>43672</v>
       </c>
-      <c r="C137" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D137" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E137" s="1">
+      <c r="C137" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E137" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="F137" s="1">
+      <c r="F137" s="12">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="G137" s="1">
+      <c r="G137" s="12">
         <v>3.1E-2</v>
       </c>
-      <c r="H137" s="4">
+      <c r="H137" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A138" s="2">
+      <c r="A138" s="8">
         <v>43646</v>
       </c>
-      <c r="B138" s="2">
+      <c r="B138" s="8">
         <v>43706</v>
       </c>
-      <c r="C138" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D138" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E138" s="1">
+      <c r="C138" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E138" s="12">
         <v>0.02</v>
       </c>
-      <c r="F138" s="1">
+      <c r="F138" s="12">
         <v>0.02</v>
       </c>
-      <c r="G138" s="1">
+      <c r="G138" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="H138" s="4">
+      <c r="H138" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A139" s="2">
+      <c r="A139" s="8">
         <v>43646</v>
       </c>
-      <c r="B139" s="2">
+      <c r="B139" s="8">
         <v>43734</v>
       </c>
-      <c r="C139" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D139" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E139" s="1">
+      <c r="C139" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E139" s="12">
         <v>0.02</v>
       </c>
-      <c r="F139" s="1">
+      <c r="F139" s="12">
         <v>0.02</v>
       </c>
-      <c r="G139" s="1">
+      <c r="G139" s="12">
         <v>0.02</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140" s="2">
+      <c r="A140" s="8">
         <v>43738</v>
       </c>
-      <c r="B140" s="2">
+      <c r="B140" s="8">
         <v>43768</v>
       </c>
-      <c r="C140" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D140" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E140" s="1">
+      <c r="C140" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E140" s="12">
         <v>1.9E-2</v>
       </c>
-      <c r="F140" s="1">
+      <c r="F140" s="12">
         <v>1.6E-2</v>
       </c>
-      <c r="G140" s="1">
+      <c r="G140" s="12">
         <v>0.02</v>
       </c>
-      <c r="H140" s="4">
+      <c r="H140" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A141" s="2">
+      <c r="A141" s="8">
         <v>43738</v>
       </c>
-      <c r="B141" s="2">
+      <c r="B141" s="8">
         <v>43796</v>
       </c>
-      <c r="C141" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D141" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E141" s="1">
+      <c r="C141" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E141" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="F141" s="1">
+      <c r="F141" s="12">
         <v>1.9E-2</v>
       </c>
-      <c r="G141" s="1">
+      <c r="G141" s="12">
         <v>1.9E-2</v>
       </c>
-      <c r="H141" s="4">
+      <c r="H141" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A142" s="2">
+      <c r="A142" s="8">
         <v>43738</v>
       </c>
-      <c r="B142" s="2">
+      <c r="B142" s="8">
         <v>43819</v>
       </c>
-      <c r="C142" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D142" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E142" s="1">
+      <c r="C142" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E142" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="F142" s="1">
+      <c r="F142" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="G142" s="1">
+      <c r="G142" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A143" s="2">
+      <c r="A143" s="8">
         <v>43830</v>
       </c>
-      <c r="B143" s="2">
+      <c r="B143" s="8">
         <v>43860</v>
       </c>
-      <c r="C143" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D143" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E143" s="1">
+      <c r="C143" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E143" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="F143" s="1">
+      <c r="F143" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="G143" s="1">
+      <c r="G143" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="H143" s="4">
+      <c r="H143" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A144" s="2">
+      <c r="A144" s="8">
         <v>43830</v>
       </c>
-      <c r="B144" s="2">
+      <c r="B144" s="8">
         <v>43888</v>
       </c>
-      <c r="C144" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D144" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E144" s="1">
+      <c r="C144" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E144" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="F144" s="1">
+      <c r="F144" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="G144" s="1">
+      <c r="G144" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="H144" s="4">
+      <c r="H144" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A145" s="2">
+      <c r="A145" s="8">
         <v>43830</v>
       </c>
-      <c r="B145" s="2">
+      <c r="B145" s="8">
         <v>43916</v>
       </c>
-      <c r="C145" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D145" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E145" s="1">
+      <c r="C145" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E145" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="F145" s="1">
+      <c r="F145" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="G145" s="1">
+      <c r="G145" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A146" s="2">
+      <c r="A146" s="8">
         <v>43921</v>
       </c>
-      <c r="B146" s="2">
+      <c r="B146" s="8">
         <v>43950</v>
       </c>
-      <c r="C146" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D146" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E146" s="1">
+      <c r="C146" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E146" s="12">
         <v>-4.8000000000000001E-2</v>
       </c>
-      <c r="F146" s="1">
+      <c r="F146" s="12">
         <v>-0.04</v>
       </c>
-      <c r="G146" s="1">
+      <c r="G146" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="H146" s="4">
+      <c r="H146" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A147" s="2">
+      <c r="A147" s="8">
         <v>43921</v>
       </c>
-      <c r="B147" s="2">
+      <c r="B147" s="8">
         <v>43979</v>
       </c>
-      <c r="C147" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D147" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E147" s="1">
+      <c r="C147" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E147" s="12">
         <v>-0.05</v>
       </c>
-      <c r="F147" s="1">
+      <c r="F147" s="12">
         <v>-4.8000000000000001E-2</v>
       </c>
-      <c r="G147" s="1">
+      <c r="G147" s="12">
         <v>-4.8000000000000001E-2</v>
       </c>
-      <c r="H147" s="4">
+      <c r="H147" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A148" s="2">
+      <c r="A148" s="8">
         <v>43921</v>
       </c>
-      <c r="B148" s="2">
+      <c r="B148" s="8">
         <v>44007</v>
       </c>
-      <c r="C148" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D148" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E148" s="1">
+      <c r="C148" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E148" s="12">
         <v>-0.05</v>
       </c>
-      <c r="F148" s="1">
+      <c r="F148" s="12">
         <v>-0.05</v>
       </c>
-      <c r="G148" s="1">
+      <c r="G148" s="12">
         <v>-0.05</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A149" s="2">
+      <c r="A149" s="8">
         <v>44012</v>
       </c>
-      <c r="B149" s="2">
+      <c r="B149" s="8">
         <v>44042</v>
       </c>
-      <c r="C149" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D149" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E149" s="1">
+      <c r="C149" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E149" s="12">
         <v>-0.32900000000000001</v>
       </c>
-      <c r="F149" s="1">
+      <c r="F149" s="12">
         <v>-0.34100000000000003</v>
       </c>
-      <c r="G149" s="1">
+      <c r="G149" s="12">
         <v>-0.05</v>
       </c>
-      <c r="H149" s="4">
+      <c r="H149" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A150" s="2">
+      <c r="A150" s="8">
         <v>44012</v>
       </c>
-      <c r="B150" s="2">
+      <c r="B150" s="8">
         <v>44070</v>
       </c>
-      <c r="C150" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D150" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E150" s="1">
+      <c r="C150" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E150" s="12">
         <v>-0.317</v>
       </c>
-      <c r="F150" s="1">
+      <c r="F150" s="12">
         <v>-0.32500000000000001</v>
       </c>
-      <c r="G150" s="1">
+      <c r="G150" s="12">
         <v>-0.32900000000000001</v>
       </c>
-      <c r="H150" s="4">
+      <c r="H150" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A151" s="2">
+      <c r="A151" s="8">
         <v>44012</v>
       </c>
-      <c r="B151" s="2">
+      <c r="B151" s="8">
         <v>44104</v>
       </c>
-      <c r="C151" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D151" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E151" s="1">
+      <c r="C151" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E151" s="12">
         <v>-0.314</v>
       </c>
-      <c r="F151" s="1">
+      <c r="F151" s="12">
         <v>-0.317</v>
       </c>
-      <c r="G151" s="1">
+      <c r="G151" s="12">
         <v>-0.317</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A152" s="2">
+      <c r="A152" s="8">
         <v>44104</v>
       </c>
-      <c r="B152" s="2">
+      <c r="B152" s="8">
         <v>44133</v>
       </c>
-      <c r="C152" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D152" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E152" s="1">
+      <c r="C152" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E152" s="12">
         <v>0.33100000000000002</v>
       </c>
-      <c r="F152" s="1">
+      <c r="F152" s="12">
         <v>0.31</v>
       </c>
-      <c r="G152" s="1">
+      <c r="G152" s="12">
         <v>-0.314</v>
       </c>
-      <c r="H152" s="4">
+      <c r="H152" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A153" s="2">
+      <c r="A153" s="8">
         <v>44104</v>
       </c>
-      <c r="B153" s="2">
+      <c r="B153" s="8">
         <v>44160</v>
       </c>
-      <c r="C153" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D153" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E153" s="1">
+      <c r="C153" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D153" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E153" s="12">
         <v>0.33100000000000002</v>
       </c>
-      <c r="F153" s="1">
+      <c r="F153" s="12">
         <v>0.33200000000000002</v>
       </c>
-      <c r="G153" s="1">
+      <c r="G153" s="12">
         <v>0.33100000000000002</v>
       </c>
-      <c r="H153" s="4">
+      <c r="H153" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A154" s="2">
+      <c r="A154" s="8">
         <v>44104</v>
       </c>
-      <c r="B154" s="2">
+      <c r="B154" s="8">
         <v>44187</v>
       </c>
-      <c r="C154" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D154" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E154" s="1">
+      <c r="C154" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D154" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E154" s="12">
         <v>0.33400000000000002</v>
       </c>
-      <c r="F154" s="1">
+      <c r="F154" s="12">
         <v>0.33100000000000002</v>
       </c>
-      <c r="G154" s="1">
+      <c r="G154" s="12">
         <v>0.33100000000000002</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A155" s="2">
+      <c r="A155" s="8">
         <v>44196</v>
       </c>
-      <c r="B155" s="2">
+      <c r="B155" s="8">
         <v>44224</v>
       </c>
-      <c r="C155" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D155" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E155" s="1">
+      <c r="C155" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D155" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E155" s="12">
         <v>0.04</v>
       </c>
-      <c r="F155" s="1">
+      <c r="F155" s="12">
         <v>0.04</v>
       </c>
-      <c r="G155" s="1">
+      <c r="G155" s="12">
         <v>0.33400000000000002</v>
       </c>
-      <c r="H155" s="4">
+      <c r="H155" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A156" s="2">
+      <c r="A156" s="8">
         <v>44196</v>
       </c>
-      <c r="B156" s="2">
+      <c r="B156" s="8">
         <v>44252</v>
       </c>
-      <c r="C156" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D156" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E156" s="1">
+      <c r="C156" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E156" s="12">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="F156" s="1">
+      <c r="F156" s="12">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="G156" s="1">
+      <c r="G156" s="12">
         <v>0.04</v>
       </c>
-      <c r="H156" s="4">
+      <c r="H156" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A157" s="2">
+      <c r="A157" s="8">
         <v>44196</v>
       </c>
-      <c r="B157" s="2">
+      <c r="B157" s="8">
         <v>44280</v>
       </c>
-      <c r="C157" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D157" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E157" s="1">
+      <c r="C157" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D157" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E157" s="12">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="F157" s="1">
+      <c r="F157" s="12">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="G157" s="1">
+      <c r="G157" s="12">
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A158" s="2">
+      <c r="A158" s="8">
         <v>44286</v>
       </c>
-      <c r="B158" s="2">
+      <c r="B158" s="8">
         <v>44315</v>
       </c>
-      <c r="C158" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D158" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E158" s="1">
+      <c r="C158" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D158" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E158" s="12">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="F158" s="1">
+      <c r="F158" s="12">
         <v>6.0999999999999999E-2</v>
       </c>
-      <c r="G158" s="1">
+      <c r="G158" s="12">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="H158" s="4">
+      <c r="H158" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A159" s="2">
+      <c r="A159" s="8">
         <v>44286</v>
       </c>
-      <c r="B159" s="2">
+      <c r="B159" s="8">
         <v>44343</v>
       </c>
-      <c r="C159" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D159" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E159" s="1">
+      <c r="C159" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D159" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E159" s="12">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="F159" s="1">
+      <c r="F159" s="12">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="G159" s="1">
+      <c r="G159" s="12">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="H159" s="4">
+      <c r="H159" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A160" s="2">
+      <c r="A160" s="8">
         <v>44286</v>
       </c>
-      <c r="B160" s="2">
+      <c r="B160" s="8">
         <v>44371</v>
       </c>
-      <c r="C160" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D160" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E160" s="1">
+      <c r="C160" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E160" s="12">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="F160" s="1">
+      <c r="F160" s="12">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="G160" s="1">
+      <c r="G160" s="12">
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A161" s="2">
+      <c r="A161" s="8">
         <v>44377</v>
       </c>
-      <c r="B161" s="2">
+      <c r="B161" s="8">
         <v>44406</v>
       </c>
-      <c r="C161" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D161" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E161" s="1">
+      <c r="C161" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E161" s="12">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="F161" s="1">
+      <c r="F161" s="12">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="G161" s="1">
+      <c r="G161" s="12">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="H161" s="4">
+      <c r="H161" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A162" s="2">
+      <c r="A162" s="8">
         <v>44377</v>
       </c>
-      <c r="B162" s="2">
+      <c r="B162" s="8">
         <v>44434</v>
       </c>
-      <c r="C162" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D162" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E162" s="1">
+      <c r="C162" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E162" s="12">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="F162" s="1">
+      <c r="F162" s="12">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="G162" s="1">
+      <c r="G162" s="12">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="H162" s="4">
+      <c r="H162" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A163" s="2">
+      <c r="A163" s="8">
         <v>44377</v>
       </c>
-      <c r="B163" s="2">
+      <c r="B163" s="8">
         <v>44469</v>
       </c>
-      <c r="C163" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D163" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E163" s="1">
+      <c r="C163" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E163" s="12">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="F163" s="1">
+      <c r="F163" s="12">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="G163" s="1">
+      <c r="G163" s="12">
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A164" s="2">
+      <c r="A164" s="8">
         <v>44469</v>
       </c>
-      <c r="B164" s="2">
+      <c r="B164" s="8">
         <v>44497</v>
       </c>
-      <c r="C164" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D164" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E164" s="1">
+      <c r="C164" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E164" s="12">
         <v>0.02</v>
       </c>
-      <c r="F164" s="1">
+      <c r="F164" s="12">
         <v>2.7E-2</v>
       </c>
-      <c r="G164" s="1">
+      <c r="G164" s="12">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="H164" s="4">
+      <c r="H164" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A165" s="2">
+      <c r="A165" s="8">
         <v>44469</v>
       </c>
-      <c r="B165" s="2">
+      <c r="B165" s="8">
         <v>44524</v>
       </c>
-      <c r="C165" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D165" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E165" s="1">
+      <c r="C165" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D165" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E165" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="F165" s="1">
+      <c r="F165" s="12">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="G165" s="1">
+      <c r="G165" s="12">
         <v>0.02</v>
       </c>
-      <c r="H165" s="4">
+      <c r="H165" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A166" s="2">
+      <c r="A166" s="8">
         <v>44469</v>
       </c>
-      <c r="B166" s="2">
+      <c r="B166" s="8">
         <v>44552</v>
       </c>
-      <c r="C166" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D166" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E166" s="1">
+      <c r="C166" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E166" s="12">
         <v>2.3E-2</v>
       </c>
-      <c r="F166" s="1">
+      <c r="F166" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="G166" s="1">
+      <c r="G166" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A167" s="2">
+      <c r="A167" s="8">
         <v>44561</v>
       </c>
-      <c r="B167" s="2">
+      <c r="B167" s="8">
         <v>44588</v>
       </c>
-      <c r="C167" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D167" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E167" s="1">
+      <c r="C167" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E167" s="12">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="F167" s="1">
+      <c r="F167" s="12">
         <v>5.5E-2</v>
       </c>
-      <c r="G167" s="1">
+      <c r="G167" s="12">
         <v>2.3E-2</v>
       </c>
-      <c r="H167" s="4">
+      <c r="H167" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A168" s="2">
+      <c r="A168" s="8">
         <v>44561</v>
       </c>
-      <c r="B168" s="2">
+      <c r="B168" s="8">
         <v>44616</v>
       </c>
-      <c r="C168" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D168" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E168" s="1">
+      <c r="C168" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D168" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E168" s="12">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F168" s="1">
+      <c r="F168" s="12">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="G168" s="1">
+      <c r="G168" s="12">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="H168" s="4">
+      <c r="H168" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A169" s="2">
+      <c r="A169" s="8">
         <v>44561</v>
       </c>
-      <c r="B169" s="2">
+      <c r="B169" s="8">
         <v>44650</v>
       </c>
-      <c r="C169" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D169" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E169" s="1">
+      <c r="C169" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D169" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E169" s="12">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="F169" s="1">
+      <c r="F169" s="12">
         <v>7.0999999999999994E-2</v>
       </c>
-      <c r="G169" s="1">
+      <c r="G169" s="12">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A170" s="2">
+      <c r="A170" s="8">
         <v>44651</v>
       </c>
-      <c r="B170" s="2">
+      <c r="B170" s="8">
         <v>44679</v>
       </c>
-      <c r="C170" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D170" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E170" s="1">
+      <c r="C170" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D170" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E170" s="12">
         <v>-1.4E-2</v>
       </c>
-      <c r="F170" s="1">
+      <c r="F170" s="12">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="G170" s="1">
+      <c r="G170" s="12">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="H170" s="4">
+      <c r="H170" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A171" s="2">
+      <c r="A171" s="8">
         <v>44651</v>
       </c>
-      <c r="B171" s="2">
+      <c r="B171" s="8">
         <v>44707</v>
       </c>
-      <c r="C171" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D171" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E171" s="1">
+      <c r="C171" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E171" s="12">
         <v>-1.4999999999999999E-2</v>
       </c>
-      <c r="F171" s="1">
+      <c r="F171" s="12">
         <v>-1.2999999999999999E-2</v>
       </c>
-      <c r="G171" s="1">
+      <c r="G171" s="12">
         <v>-1.4E-2</v>
       </c>
-      <c r="H171" s="4">
+      <c r="H171" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A172" s="2">
+      <c r="A172" s="8">
         <v>44651</v>
       </c>
-      <c r="B172" s="2">
+      <c r="B172" s="8">
         <v>44741</v>
       </c>
-      <c r="C172" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D172" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E172" s="1">
+      <c r="C172" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E172" s="12">
         <v>-1.6E-2</v>
       </c>
-      <c r="F172" s="1">
+      <c r="F172" s="12">
         <v>-1.4999999999999999E-2</v>
       </c>
-      <c r="G172" s="1">
+      <c r="G172" s="12">
         <v>-1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A173" s="2">
+      <c r="A173" s="8">
         <v>44742</v>
       </c>
-      <c r="B173" s="2">
+      <c r="B173" s="8">
         <v>44770</v>
       </c>
-      <c r="C173" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D173" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E173" s="1">
+      <c r="C173" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D173" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E173" s="12">
         <v>-8.9999999999999993E-3</v>
       </c>
-      <c r="F173" s="1">
+      <c r="F173" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G173" s="1">
+      <c r="G173" s="12">
         <v>-1.6E-2</v>
       </c>
-      <c r="H173" s="4">
+      <c r="H173" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A174" s="2">
+      <c r="A174" s="8">
         <v>44742</v>
       </c>
-      <c r="B174" s="2">
+      <c r="B174" s="8">
         <v>44798</v>
       </c>
-      <c r="C174" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D174" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E174" s="1">
+      <c r="C174" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D174" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E174" s="12">
         <v>-6.0000000000000001E-3</v>
       </c>
-      <c r="F174" s="1">
+      <c r="F174" s="12">
         <v>-8.0000000000000002E-3</v>
       </c>
-      <c r="G174" s="1">
+      <c r="G174" s="12">
         <v>-8.9999999999999993E-3</v>
       </c>
-      <c r="H174" s="4">
+      <c r="H174" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A175" s="2">
+      <c r="A175" s="8">
         <v>44742</v>
       </c>
-      <c r="B175" s="2">
+      <c r="B175" s="8">
         <v>44833</v>
       </c>
-      <c r="C175" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D175" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E175" s="1">
+      <c r="C175" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E175" s="12">
         <v>-6.0000000000000001E-3</v>
       </c>
-      <c r="F175" s="1">
+      <c r="F175" s="12">
         <v>-6.0000000000000001E-3</v>
       </c>
-      <c r="G175" s="1">
+      <c r="G175" s="12">
         <v>-1.6E-2</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A176" s="2">
+      <c r="A176" s="8">
         <v>44834</v>
       </c>
-      <c r="B176" s="2">
+      <c r="B176" s="8">
         <v>44861</v>
       </c>
-      <c r="C176" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D176" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E176" s="1">
+      <c r="C176" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D176" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E176" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="F176" s="1">
+      <c r="F176" s="12">
         <v>2.4E-2</v>
       </c>
-      <c r="G176" s="1">
+      <c r="G176" s="12">
         <v>-6.0000000000000001E-3</v>
       </c>
-      <c r="H176" s="4">
+      <c r="H176" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A177" s="2">
+      <c r="A177" s="8">
         <v>44834</v>
       </c>
-      <c r="B177" s="2">
+      <c r="B177" s="8">
         <v>44895</v>
       </c>
-      <c r="C177" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D177" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E177" s="1">
+      <c r="C177" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D177" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E177" s="12">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="F177" s="1">
+      <c r="F177" s="12">
         <v>2.7E-2</v>
       </c>
-      <c r="G177" s="1">
+      <c r="G177" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="H177" s="4">
+      <c r="H177" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A178" s="2">
+      <c r="A178" s="8">
         <v>44834</v>
       </c>
-      <c r="B178" s="2">
+      <c r="B178" s="8">
         <v>44917</v>
       </c>
-      <c r="C178" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D178" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E178" s="1">
+      <c r="C178" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E178" s="12">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="F178" s="1">
+      <c r="F178" s="12">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="G178" s="1">
+      <c r="G178" s="12">
         <v>-6.0000000000000001E-3</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A179" s="2">
+      <c r="A179" s="8">
         <v>44926</v>
       </c>
-      <c r="B179" s="2">
+      <c r="B179" s="8">
         <v>44952</v>
       </c>
-      <c r="C179" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D179" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E179" s="1">
+      <c r="C179" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D179" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E179" s="12">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="F179" s="1">
+      <c r="F179" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="G179" s="1">
+      <c r="G179" s="12">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="H179" s="4">
+      <c r="H179" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A180" s="2">
+      <c r="A180" s="8">
         <v>44926</v>
       </c>
-      <c r="B180" s="2">
+      <c r="B180" s="8">
         <v>44980</v>
       </c>
-      <c r="C180" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D180" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E180" s="1">
+      <c r="C180" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D180" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E180" s="12">
         <v>2.7E-2</v>
       </c>
-      <c r="F180" s="1">
+      <c r="F180" s="12">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="G180" s="1">
+      <c r="G180" s="12">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="H180" s="4">
+      <c r="H180" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A181" s="2">
+      <c r="A181" s="8">
         <v>44926</v>
       </c>
-      <c r="B181" s="2">
+      <c r="B181" s="8">
         <v>45015</v>
       </c>
-      <c r="C181" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D181" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E181" s="1">
+      <c r="C181" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D181" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E181" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="F181" s="1">
+      <c r="F181" s="12">
         <v>2.7E-2</v>
       </c>
-      <c r="G181" s="1">
+      <c r="G181" s="12">
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A182" s="2">
+      <c r="A182" s="8">
         <v>45016</v>
       </c>
-      <c r="B182" s="2">
+      <c r="B182" s="8">
         <v>45043</v>
       </c>
-      <c r="C182" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D182" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E182" s="1">
+      <c r="C182" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D182" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E182" s="12">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="F182" s="1">
+      <c r="F182" s="12">
         <v>0.02</v>
       </c>
-      <c r="G182" s="1">
+      <c r="G182" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="H182" s="4">
+      <c r="H182" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A183" s="2">
+      <c r="A183" s="8">
         <v>45016</v>
       </c>
-      <c r="B183" s="2">
+      <c r="B183" s="8">
         <v>45071</v>
       </c>
-      <c r="C183" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D183" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E183" s="1">
+      <c r="C183" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E183" s="12">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="F183" s="1">
+      <c r="F183" s="12">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="G183" s="1">
+      <c r="G183" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="H183" s="4">
+      <c r="H183" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A184" s="2">
+      <c r="A184" s="8">
         <v>45016</v>
       </c>
-      <c r="B184" s="2">
+      <c r="B184" s="8">
         <v>45106</v>
       </c>
-      <c r="C184" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D184" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E184" s="1">
+      <c r="C184" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E184" s="12">
         <v>0.02</v>
       </c>
-      <c r="F184" s="1">
+      <c r="F184" s="12">
         <v>1.4E-2</v>
       </c>
-      <c r="G184" s="1">
+      <c r="G184" s="12">
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A185" s="2">
+      <c r="A185" s="8">
         <v>45107</v>
       </c>
-      <c r="B185" s="2">
+      <c r="B185" s="8">
         <v>45134</v>
       </c>
-      <c r="C185" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D185" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E185" s="1">
+      <c r="C185" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D185" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E185" s="12">
         <v>2.4E-2</v>
       </c>
-      <c r="F185" s="1">
+      <c r="F185" s="12">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="G185" s="1">
+      <c r="G185" s="12">
         <v>0.02</v>
       </c>
-      <c r="H185" s="4">
+      <c r="H185" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A186" s="2">
+      <c r="A186" s="8">
         <v>45107</v>
       </c>
-      <c r="B186" s="2">
+      <c r="B186" s="8">
         <v>45168</v>
       </c>
-      <c r="C186" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D186" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E186" s="1">
+      <c r="C186" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D186" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E186" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="F186" s="1">
+      <c r="F186" s="12">
         <v>2.4E-2</v>
       </c>
-      <c r="G186" s="1">
+      <c r="G186" s="12">
         <v>0.02</v>
       </c>
-      <c r="H186" s="4">
+      <c r="H186" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A187" s="2">
+      <c r="A187" s="8">
         <v>45107</v>
       </c>
-      <c r="B187" s="2">
+      <c r="B187" s="8">
         <v>45197</v>
       </c>
-      <c r="C187" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D187" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E187" s="1">
+      <c r="C187" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D187" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E187" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="F187" s="1">
+      <c r="F187" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="G187" s="1">
+      <c r="G187" s="12">
         <v>0.02</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A188" s="2">
+      <c r="A188" s="8">
         <v>45199</v>
       </c>
-      <c r="B188" s="2">
+      <c r="B188" s="8">
         <v>45225</v>
       </c>
-      <c r="C188" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D188" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E188" s="1">
+      <c r="C188" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D188" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E188" s="12">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="F188" s="1">
+      <c r="F188" s="12">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="G188" s="1">
+      <c r="G188" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="H188" s="4">
+      <c r="H188" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A189" s="2">
+      <c r="A189" s="8">
         <v>45199</v>
       </c>
-      <c r="B189" s="2">
+      <c r="B189" s="8">
         <v>45259</v>
       </c>
-      <c r="C189" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D189" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E189" s="1">
+      <c r="C189" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D189" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E189" s="12">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="F189" s="1">
+      <c r="F189" s="12">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="G189" s="1">
+      <c r="G189" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="H189" s="4">
+      <c r="H189" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A190" s="2">
+      <c r="A190" s="8">
         <v>45199</v>
       </c>
-      <c r="B190" s="2">
+      <c r="B190" s="8">
         <v>45281</v>
       </c>
-      <c r="C190" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D190" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E190" s="1">
+      <c r="C190" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D190" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E190" s="12">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="F190" s="1">
+      <c r="F190" s="12">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="G190" s="1">
+      <c r="G190" s="12">
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A191" s="2">
+      <c r="A191" s="8">
         <v>45291</v>
       </c>
-      <c r="B191" s="2">
+      <c r="B191" s="8">
         <v>45316</v>
       </c>
-      <c r="C191" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D191" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E191" s="1">
+      <c r="C191" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D191" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E191" s="12">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="F191" s="1">
+      <c r="F191" s="12">
         <v>0.02</v>
       </c>
-      <c r="G191" s="1">
+      <c r="G191" s="12">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="H191" s="4">
+      <c r="H191" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A192" s="2">
+      <c r="A192" s="8">
         <v>45291</v>
       </c>
-      <c r="B192" s="2">
+      <c r="B192" s="8">
         <v>45350</v>
       </c>
-      <c r="C192" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D192" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E192" s="1">
+      <c r="C192" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D192" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E192" s="12">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="F192" s="1">
+      <c r="F192" s="12">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="G192" s="1">
+      <c r="G192" s="12">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="H192" s="4">
+      <c r="H192" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A193" s="2">
+      <c r="A193" s="8">
         <v>45291</v>
       </c>
-      <c r="B193" s="2">
+      <c r="B193" s="8">
         <v>45379</v>
       </c>
-      <c r="C193" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D193" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E193" s="1">
+      <c r="C193" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D193" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E193" s="12">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="F193" s="1">
+      <c r="F193" s="12">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="G193" s="1">
+      <c r="G193" s="12">
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A194" s="2">
+      <c r="A194" s="8">
         <v>45382</v>
       </c>
-      <c r="B194" s="2">
+      <c r="B194" s="8">
         <v>45407</v>
       </c>
-      <c r="C194" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D194" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E194" s="1">
+      <c r="C194" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D194" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E194" s="12">
         <v>1.6E-2</v>
       </c>
-      <c r="F194" s="1">
+      <c r="F194" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G194" s="1">
+      <c r="G194" s="12">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="H194" s="4">
+      <c r="H194" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A195" s="2">
+      <c r="A195" s="8">
         <v>45382</v>
       </c>
-      <c r="B195" s="2">
+      <c r="B195" s="8">
         <v>45442</v>
       </c>
-      <c r="C195" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D195" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E195" s="1">
+      <c r="C195" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D195" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E195" s="12">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="F195" s="1">
+      <c r="F195" s="12">
         <v>1.6E-2</v>
       </c>
-      <c r="G195" s="1">
+      <c r="G195" s="12">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="H195" s="4">
+      <c r="H195" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A196" s="2">
+      <c r="A196" s="8">
         <v>45382</v>
       </c>
-      <c r="B196" s="2">
+      <c r="B196" s="8">
         <v>45470</v>
       </c>
-      <c r="C196" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D196" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E196" s="1">
+      <c r="C196" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D196" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E196" s="12">
         <v>1.4E-2</v>
       </c>
-      <c r="F196" s="1">
+      <c r="F196" s="12">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="G196" s="1">
+      <c r="G196" s="12">
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A197" s="2">
+      <c r="A197" s="8">
         <v>45473</v>
       </c>
-      <c r="B197" s="2">
+      <c r="B197" s="8">
         <v>45498</v>
       </c>
-      <c r="C197" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D197" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E197" s="1">
+      <c r="C197" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D197" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E197" s="12">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="F197" s="1">
+      <c r="F197" s="12">
         <v>0.02</v>
       </c>
-      <c r="G197" s="1">
+      <c r="G197" s="12">
         <v>1.4E-2</v>
       </c>
-      <c r="H197" s="4">
+      <c r="H197" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A198" s="2">
+      <c r="A198" s="8">
         <v>45473</v>
       </c>
-      <c r="B198" s="2">
+      <c r="B198" s="8">
         <v>45533</v>
       </c>
-      <c r="C198" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D198" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E198" s="1">
+      <c r="C198" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D198" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E198" s="12">
         <v>0.03</v>
       </c>
-      <c r="F198" s="1">
+      <c r="F198" s="12">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="G198" s="1">
+      <c r="G198" s="12">
         <v>1.4E-2</v>
       </c>
-      <c r="H198" s="4">
+      <c r="H198" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A199" s="2">
+      <c r="A199" s="8">
         <v>45473</v>
       </c>
-      <c r="B199" s="2">
+      <c r="B199" s="8">
         <v>45561</v>
       </c>
-      <c r="C199" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D199" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E199" s="1">
+      <c r="C199" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D199" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E199" s="12">
         <v>0.03</v>
       </c>
-      <c r="F199" s="1">
+      <c r="F199" s="12">
         <v>0.03</v>
       </c>
-      <c r="G199" s="1">
+      <c r="G199" s="12">
         <v>1.6E-2</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A200" s="2">
+      <c r="A200" s="8">
         <v>45565</v>
       </c>
-      <c r="B200" s="2">
+      <c r="B200" s="8">
         <v>45595</v>
       </c>
-      <c r="C200" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D200" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E200" s="1">
+      <c r="C200" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D200" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E200" s="12">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="F200" s="1">
+      <c r="F200" s="12">
         <v>0.03</v>
       </c>
-      <c r="G200" s="1">
+      <c r="G200" s="12">
         <v>0.03</v>
       </c>
-      <c r="H200" s="4">
+      <c r="H200" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A201" s="2">
+      <c r="A201" s="8">
         <v>45565</v>
       </c>
-      <c r="B201" s="2">
+      <c r="B201" s="8">
         <v>45623</v>
       </c>
-      <c r="C201" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D201" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E201" s="1">
+      <c r="C201" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D201" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E201" s="12">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="F201" s="1">
+      <c r="F201" s="12">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="G201" s="1">
+      <c r="G201" s="12">
         <v>0.03</v>
       </c>
-      <c r="H201" s="4">
+      <c r="H201" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A202" s="2">
+      <c r="A202" s="8">
         <v>45565</v>
       </c>
-      <c r="B202" s="2">
+      <c r="B202" s="8">
         <v>45645</v>
       </c>
-      <c r="C202" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D202" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E202" s="1">
+      <c r="C202" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D202" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E202" s="12">
         <v>3.1E-2</v>
       </c>
-      <c r="F202" s="1">
+      <c r="F202" s="12">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="G202" s="1">
+      <c r="G202" s="12">
         <v>0.03</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A203" s="2">
+      <c r="A203" s="8">
         <v>45657</v>
       </c>
-      <c r="B203" s="2">
+      <c r="B203" s="8">
         <v>45687</v>
       </c>
-      <c r="C203" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D203" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E203" s="1">
+      <c r="C203" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D203" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E203" s="12">
         <v>2.3E-2</v>
       </c>
-      <c r="F203" s="1">
+      <c r="F203" s="12">
         <v>2.7E-2</v>
       </c>
-      <c r="G203" s="1">
+      <c r="G203" s="12">
         <v>3.1E-2</v>
       </c>
-      <c r="H203" s="4">
+      <c r="H203" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A204" s="2">
+      <c r="A204" s="8">
         <v>45657</v>
       </c>
-      <c r="B204" s="2">
+      <c r="B204" s="8">
         <v>45715</v>
       </c>
-      <c r="C204" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D204" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E204" s="1">
+      <c r="C204" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D204" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E204" s="12">
         <v>2.3E-2</v>
       </c>
-      <c r="F204" s="1">
+      <c r="F204" s="12">
         <v>2.3E-2</v>
       </c>
-      <c r="G204" s="1">
+      <c r="G204" s="12">
         <v>3.1E-2</v>
       </c>
-      <c r="H204" s="4">
+      <c r="H204" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A205" s="2">
+      <c r="A205" s="8">
         <v>45657</v>
       </c>
-      <c r="B205" s="2">
+      <c r="B205" s="8">
         <v>45743</v>
       </c>
-      <c r="C205" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D205" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E205" s="1">
+      <c r="C205" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D205" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E205" s="12">
         <v>2.4E-2</v>
       </c>
-      <c r="F205" s="1">
+      <c r="F205" s="12">
         <v>2.3E-2</v>
       </c>
-      <c r="G205" s="1">
+      <c r="G205" s="12">
         <v>3.1E-2</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A206" s="2">
+      <c r="A206" s="8">
         <v>45747</v>
       </c>
-      <c r="B206" s="2">
+      <c r="B206" s="8">
         <v>45777</v>
       </c>
-      <c r="C206" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D206" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E206" s="1">
+      <c r="C206" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D206" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E206" s="12">
         <v>-3.0000000000000001E-3</v>
       </c>
-      <c r="F206" s="1">
+      <c r="F206" s="12">
         <v>2E-3</v>
       </c>
-      <c r="G206" s="1">
+      <c r="G206" s="12">
         <v>2.4E-2</v>
       </c>
-      <c r="H206" s="4">
+      <c r="H206" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A207" s="2">
+      <c r="A207" s="8">
         <v>45747</v>
       </c>
-      <c r="B207" s="2">
+      <c r="B207" s="8">
         <v>45806</v>
       </c>
-      <c r="C207" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D207" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E207" s="1">
+      <c r="C207" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D207" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E207" s="12">
         <v>-2E-3</v>
       </c>
-      <c r="F207" s="1">
+      <c r="F207" s="12">
         <v>-3.0000000000000001E-3</v>
       </c>
-      <c r="G207" s="1">
+      <c r="G207" s="12">
         <v>2.4E-2</v>
       </c>
-      <c r="H207" s="4">
+      <c r="H207" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A208" s="2">
+      <c r="A208" s="8">
         <v>45747</v>
       </c>
-      <c r="B208" s="2">
+      <c r="B208" s="8">
         <v>45834</v>
       </c>
-      <c r="C208" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D208" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E208" s="1">
+      <c r="C208" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D208" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E208" s="12">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="F208" s="1">
+      <c r="F208" s="12">
         <v>-2E-3</v>
       </c>
-      <c r="G208" s="1">
+      <c r="G208" s="12">
         <v>2.4E-2</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A209" s="2">
+      <c r="A209" s="8">
         <v>45838</v>
       </c>
-      <c r="B209" s="2">
+      <c r="B209" s="8">
         <v>45868</v>
       </c>
-      <c r="C209" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D209" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E209" s="1">
+      <c r="C209" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D209" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E209" s="12">
         <v>0.03</v>
       </c>
-      <c r="F209" s="1">
+      <c r="F209" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G209" s="1">
+      <c r="G209" s="12">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="H209" s="4">
+      <c r="H209" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A210" s="2">
+      <c r="A210" s="8">
         <v>45838</v>
       </c>
-      <c r="B210" s="2">
+      <c r="B210" s="8">
         <v>45897</v>
       </c>
-      <c r="C210" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D210" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E210" s="1">
+      <c r="C210" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D210" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E210" s="12">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="F210" s="1">
+      <c r="F210" s="12">
         <v>0.03</v>
       </c>
-      <c r="G210" s="1">
+      <c r="G210" s="12">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="H210" s="4">
+      <c r="H210" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A211" s="2">
+      <c r="A211" s="8">
         <v>45838</v>
       </c>
-      <c r="B211" s="2">
+      <c r="B211" s="8">
         <v>45925</v>
       </c>
-      <c r="C211" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D211" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E211" s="1">
+      <c r="C211" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D211" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E211" s="12">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="F211" s="1">
+      <c r="F211" s="12">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="G211" s="1">
+      <c r="G211" s="12">
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A212" s="2">
+      <c r="A212" s="8">
         <v>45930</v>
       </c>
-      <c r="B212" s="2">
+      <c r="B212" s="8">
         <v>46014</v>
       </c>
-      <c r="C212" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D212" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E212" s="1">
+      <c r="C212" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D212" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E212" s="12">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="F212" s="1">
+      <c r="F212" s="12">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="G212" s="1">
+      <c r="G212" s="12">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="H212" s="4">
+      <c r="H212" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213" s="8">
+        <v>45930</v>
+      </c>
+      <c r="B213" s="8">
+        <v>46044</v>
+      </c>
+      <c r="C213" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D213" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E213" s="12">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="F213" s="12">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="G213" s="12">
+        <v>3.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A214" s="8">
+        <v>46022</v>
+      </c>
+      <c r="B214" s="8">
+        <v>46073</v>
+      </c>
+      <c r="C214" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D214" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E214" s="12">
+        <v>1.4E-2</v>
+      </c>
+      <c r="F214" s="12">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="G214" s="12">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="H214" s="7">
         <v>1</v>
       </c>
     </row>
@@ -5794,7 +5873,7 @@
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5804,7 +5883,7 @@
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">

--- a/data/macro/USA/USGDP.xlsx
+++ b/data/macro/USA/USGDP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FE2BD7-832F-4B59-A348-892FB48AE6F9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E9FB8D-DCC5-4A8B-B095-013A5E4CFB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" xr2:uid="{DF730CA5-B386-4F44-87DF-4B36E64B9A15}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF730CA5-B386-4F44-87DF-4B36E64B9A15}"/>
   </bookViews>
   <sheets>
     <sheet name="USGDP" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="12">
   <si>
     <t>Release Date</t>
   </si>
@@ -55,9 +55,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.investing.com/economic-calendar/gdp-375</t>
-  </si>
-  <si>
     <t>Time Zone</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -66,6 +63,10 @@
   </si>
   <si>
     <t>UTC-4</t>
+  </si>
+  <si>
+    <t>https://www.investing.com/economic-calendar/gdp-375</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -76,10 +77,10 @@
     <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="181" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="182" formatCode="0.0%"/>
+    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="180" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -121,6 +122,14 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -139,7 +148,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -149,8 +158,11 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -178,23 +190,27 @@
     <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
     <cellStyle name="쉼표" xfId="1" builtinId="3"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="3" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -506,20 +522,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00FCE0E7-6C64-48A0-8BF6-812467A264DB}">
-  <dimension ref="A1:H214"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H216"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="14.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="14.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" style="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="5"/>
+    <col min="8" max="8" width="11.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -530,7 +546,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1" s="11" t="s">
         <v>2</v>
@@ -545,7 +561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="8">
         <v>39447</v>
       </c>
@@ -556,7 +572,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" s="12">
         <v>6.0000000000000001E-3</v>
@@ -571,7 +587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="8">
         <v>39447</v>
       </c>
@@ -582,7 +598,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" s="12">
         <v>6.0000000000000001E-3</v>
@@ -594,7 +610,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="8">
         <v>39538</v>
       </c>
@@ -605,7 +621,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E4" s="12">
         <v>6.0000000000000001E-3</v>
@@ -620,7 +636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="8">
         <v>39538</v>
       </c>
@@ -631,7 +647,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" s="12">
         <v>2.7E-2</v>
@@ -643,7 +659,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
         <v>39629</v>
       </c>
@@ -654,7 +670,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" s="12">
         <v>1.9E-2</v>
@@ -669,7 +685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="8">
         <v>39629</v>
       </c>
@@ -680,7 +696,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" s="12">
         <v>3.3000000000000002E-2</v>
@@ -695,7 +711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="8">
         <v>39629</v>
       </c>
@@ -706,7 +722,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" s="12">
         <v>2.8000000000000001E-2</v>
@@ -718,7 +734,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>39721</v>
       </c>
@@ -729,7 +745,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" s="12">
         <v>-3.0000000000000001E-3</v>
@@ -744,7 +760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
         <v>39721</v>
       </c>
@@ -755,7 +771,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" s="12">
         <v>-5.0000000000000001E-3</v>
@@ -770,7 +786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="8">
         <v>39721</v>
       </c>
@@ -781,7 +797,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" s="12">
         <v>-5.0000000000000001E-3</v>
@@ -793,7 +809,7 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="8">
         <v>39813</v>
       </c>
@@ -804,7 +820,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" s="12">
         <v>-3.7999999999999999E-2</v>
@@ -819,7 +835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="8">
         <v>39813</v>
       </c>
@@ -830,7 +846,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" s="12">
         <v>-6.2E-2</v>
@@ -845,7 +861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="8">
         <v>39813</v>
       </c>
@@ -856,7 +872,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E14" s="12">
         <v>-6.3E-2</v>
@@ -868,7 +884,7 @@
         <v>-6.2E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="8">
         <v>39903</v>
       </c>
@@ -879,7 +895,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15" s="12">
         <v>-6.0999999999999999E-2</v>
@@ -894,7 +910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="8">
         <v>39903</v>
       </c>
@@ -905,7 +921,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E16" s="12">
         <v>-5.7000000000000002E-2</v>
@@ -920,7 +936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="8">
         <v>39903</v>
       </c>
@@ -931,7 +947,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E17" s="12">
         <v>-5.5E-2</v>
@@ -943,7 +959,7 @@
         <v>-5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="8">
         <v>39994</v>
       </c>
@@ -954,7 +970,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E18" s="12">
         <v>-0.01</v>
@@ -969,7 +985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="8">
         <v>39994</v>
       </c>
@@ -980,7 +996,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" s="12">
         <v>-0.01</v>
@@ -995,7 +1011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="8">
         <v>39994</v>
       </c>
@@ -1006,7 +1022,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E20" s="12">
         <v>-7.0000000000000001E-3</v>
@@ -1018,7 +1034,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="8">
         <v>40086</v>
       </c>
@@ -1029,7 +1045,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E21" s="12">
         <v>3.5000000000000003E-2</v>
@@ -1044,7 +1060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="8">
         <v>40086</v>
       </c>
@@ -1055,7 +1071,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22" s="12">
         <v>2.8000000000000001E-2</v>
@@ -1070,7 +1086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="8">
         <v>40086</v>
       </c>
@@ -1081,7 +1097,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E23" s="12">
         <v>2.1999999999999999E-2</v>
@@ -1093,7 +1109,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="8">
         <v>40178</v>
       </c>
@@ -1104,7 +1120,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E24" s="12">
         <v>5.7000000000000002E-2</v>
@@ -1119,7 +1135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="8">
         <v>40178</v>
       </c>
@@ -1130,7 +1146,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25" s="12">
         <v>5.8999999999999997E-2</v>
@@ -1145,7 +1161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="8">
         <v>40178</v>
       </c>
@@ -1156,7 +1172,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E26" s="12">
         <v>5.6000000000000001E-2</v>
@@ -1168,7 +1184,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="8">
         <v>40268</v>
       </c>
@@ -1179,7 +1195,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E27" s="12">
         <v>3.2000000000000001E-2</v>
@@ -1194,7 +1210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="8">
         <v>40268</v>
       </c>
@@ -1205,7 +1221,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E28" s="12">
         <v>0.03</v>
@@ -1220,7 +1236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="8">
         <v>40268</v>
       </c>
@@ -1231,7 +1247,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E29" s="12">
         <v>2.7E-2</v>
@@ -1243,7 +1259,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="8">
         <v>40359</v>
       </c>
@@ -1254,7 +1270,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E30" s="12">
         <v>2.4E-2</v>
@@ -1269,7 +1285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="8">
         <v>40359</v>
       </c>
@@ -1280,7 +1296,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E31" s="12">
         <v>1.6E-2</v>
@@ -1295,7 +1311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="8">
         <v>40359</v>
       </c>
@@ -1306,7 +1322,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E32" s="12">
         <v>1.7000000000000001E-2</v>
@@ -1318,7 +1334,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="8">
         <v>40451</v>
       </c>
@@ -1329,7 +1345,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E33" s="12">
         <v>0.02</v>
@@ -1344,7 +1360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="8">
         <v>40451</v>
       </c>
@@ -1355,7 +1371,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E34" s="12">
         <v>2.5000000000000001E-2</v>
@@ -1370,7 +1386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="8">
         <v>40451</v>
       </c>
@@ -1381,7 +1397,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E35" s="12">
         <v>2.5999999999999999E-2</v>
@@ -1393,7 +1409,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="8">
         <v>40543</v>
       </c>
@@ -1404,7 +1420,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E36" s="12">
         <v>3.2000000000000001E-2</v>
@@ -1419,7 +1435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="8">
         <v>40543</v>
       </c>
@@ -1430,7 +1446,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E37" s="12">
         <v>2.8000000000000001E-2</v>
@@ -1445,7 +1461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="8">
         <v>40543</v>
       </c>
@@ -1456,7 +1472,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E38" s="12">
         <v>3.1E-2</v>
@@ -1468,7 +1484,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="8">
         <v>40633</v>
       </c>
@@ -1479,7 +1495,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E39" s="12">
         <v>1.7999999999999999E-2</v>
@@ -1494,7 +1510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="8">
         <v>40633</v>
       </c>
@@ -1505,7 +1521,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E40" s="12">
         <v>1.7999999999999999E-2</v>
@@ -1520,7 +1536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="8">
         <v>40633</v>
       </c>
@@ -1531,7 +1547,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E41" s="12">
         <v>1.9E-2</v>
@@ -1543,7 +1559,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="8">
         <v>40724</v>
       </c>
@@ -1554,7 +1570,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E42" s="12">
         <v>1.2999999999999999E-2</v>
@@ -1569,7 +1585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="8">
         <v>40724</v>
       </c>
@@ -1580,7 +1596,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E43" s="12">
         <v>0.01</v>
@@ -1595,7 +1611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="8">
         <v>40724</v>
       </c>
@@ -1606,7 +1622,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E44" s="12">
         <v>1.2999999999999999E-2</v>
@@ -1618,7 +1634,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="8">
         <v>40816</v>
       </c>
@@ -1629,7 +1645,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E45" s="12">
         <v>2.5000000000000001E-2</v>
@@ -1644,7 +1660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="8">
         <v>40816</v>
       </c>
@@ -1655,7 +1671,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E46" s="12">
         <v>0.02</v>
@@ -1670,7 +1686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="8">
         <v>40816</v>
       </c>
@@ -1681,7 +1697,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E47" s="12">
         <v>1.7999999999999999E-2</v>
@@ -1693,7 +1709,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="8">
         <v>40908</v>
       </c>
@@ -1704,7 +1720,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E48" s="12">
         <v>2.8000000000000001E-2</v>
@@ -1719,7 +1735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="8">
         <v>40908</v>
       </c>
@@ -1730,7 +1746,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E49" s="12">
         <v>0.03</v>
@@ -1745,7 +1761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="8">
         <v>40908</v>
       </c>
@@ -1756,7 +1772,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E50" s="12">
         <v>0.03</v>
@@ -1768,7 +1784,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="8">
         <v>40999</v>
       </c>
@@ -1779,7 +1795,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E51" s="12">
         <v>2.1999999999999999E-2</v>
@@ -1794,7 +1810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="8">
         <v>40999</v>
       </c>
@@ -1805,7 +1821,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E52" s="12">
         <v>1.9E-2</v>
@@ -1820,7 +1836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="8">
         <v>40999</v>
       </c>
@@ -1831,7 +1847,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E53" s="12">
         <v>1.9E-2</v>
@@ -1843,7 +1859,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="8">
         <v>41090</v>
       </c>
@@ -1854,7 +1870,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E54" s="12">
         <v>1.4999999999999999E-2</v>
@@ -1869,7 +1885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="8">
         <v>41090</v>
       </c>
@@ -1880,7 +1896,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E55" s="12">
         <v>1.7000000000000001E-2</v>
@@ -1895,7 +1911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" s="8">
         <v>41090</v>
       </c>
@@ -1906,7 +1922,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E56" s="12">
         <v>1.2999999999999999E-2</v>
@@ -1918,7 +1934,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="8">
         <v>41182</v>
       </c>
@@ -1929,7 +1945,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E57" s="12">
         <v>0.02</v>
@@ -1944,7 +1960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" s="8">
         <v>41182</v>
       </c>
@@ -1955,7 +1971,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E58" s="12">
         <v>2.7E-2</v>
@@ -1970,7 +1986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" s="8">
         <v>41182</v>
       </c>
@@ -1981,7 +1997,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E59" s="12">
         <v>3.1E-2</v>
@@ -1993,7 +2009,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="8">
         <v>41274</v>
       </c>
@@ -2004,7 +2020,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E60" s="12">
         <v>-1E-3</v>
@@ -2019,7 +2035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="8">
         <v>41274</v>
       </c>
@@ -2030,7 +2046,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E61" s="12">
         <v>1E-3</v>
@@ -2045,7 +2061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" s="8">
         <v>41274</v>
       </c>
@@ -2056,7 +2072,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E62" s="12">
         <v>4.0000000000000001E-3</v>
@@ -2068,7 +2084,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" s="8">
         <v>41364</v>
       </c>
@@ -2079,7 +2095,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E63" s="12">
         <v>2.5000000000000001E-2</v>
@@ -2094,7 +2110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" s="8">
         <v>41364</v>
       </c>
@@ -2105,7 +2121,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E64" s="12">
         <v>2.4E-2</v>
@@ -2120,7 +2136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="8">
         <v>41364</v>
       </c>
@@ -2131,7 +2147,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E65" s="12">
         <v>1.7999999999999999E-2</v>
@@ -2143,7 +2159,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" s="8">
         <v>41455</v>
       </c>
@@ -2154,7 +2170,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E66" s="12">
         <v>1.7000000000000001E-2</v>
@@ -2169,7 +2185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="8">
         <v>41455</v>
       </c>
@@ -2180,7 +2196,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E67" s="12">
         <v>2.5000000000000001E-2</v>
@@ -2195,7 +2211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" s="8">
         <v>41455</v>
       </c>
@@ -2206,7 +2222,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E68" s="12">
         <v>2.5000000000000001E-2</v>
@@ -2218,7 +2234,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="8">
         <v>41547</v>
       </c>
@@ -2229,7 +2245,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E69" s="12">
         <v>2.8000000000000001E-2</v>
@@ -2244,7 +2260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="8">
         <v>41547</v>
       </c>
@@ -2255,7 +2271,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E70" s="12">
         <v>3.5999999999999997E-2</v>
@@ -2270,7 +2286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="8">
         <v>41547</v>
       </c>
@@ -2281,7 +2297,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E71" s="12">
         <v>4.1000000000000002E-2</v>
@@ -2293,7 +2309,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="8">
         <v>41639</v>
       </c>
@@ -2304,7 +2320,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E72" s="12">
         <v>3.2000000000000001E-2</v>
@@ -2319,7 +2335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" s="8">
         <v>41639</v>
       </c>
@@ -2330,7 +2346,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E73" s="12">
         <v>2.4E-2</v>
@@ -2345,7 +2361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="8">
         <v>41639</v>
       </c>
@@ -2356,7 +2372,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E74" s="12">
         <v>2.5999999999999999E-2</v>
@@ -2368,7 +2384,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="8">
         <v>41729</v>
       </c>
@@ -2379,7 +2395,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E75" s="12">
         <v>1E-3</v>
@@ -2394,7 +2410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="8">
         <v>41729</v>
       </c>
@@ -2405,7 +2421,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E76" s="12">
         <v>-0.01</v>
@@ -2420,7 +2436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="8">
         <v>41729</v>
       </c>
@@ -2431,7 +2447,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E77" s="12">
         <v>-2.9000000000000001E-2</v>
@@ -2443,7 +2459,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" s="8">
         <v>41820</v>
       </c>
@@ -2454,7 +2470,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E78" s="12">
         <v>0.04</v>
@@ -2469,7 +2485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="8">
         <v>41820</v>
       </c>
@@ -2480,7 +2496,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E79" s="12">
         <v>4.2000000000000003E-2</v>
@@ -2495,7 +2511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="8">
         <v>41820</v>
       </c>
@@ -2506,7 +2522,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E80" s="12">
         <v>4.5999999999999999E-2</v>
@@ -2518,7 +2534,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" s="8">
         <v>41912</v>
       </c>
@@ -2529,7 +2545,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E81" s="12">
         <v>3.5000000000000003E-2</v>
@@ -2544,7 +2560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" s="8">
         <v>41912</v>
       </c>
@@ -2555,7 +2571,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E82" s="12">
         <v>3.9E-2</v>
@@ -2570,7 +2586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" s="8">
         <v>41912</v>
       </c>
@@ -2581,7 +2597,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E83" s="12">
         <v>0.05</v>
@@ -2593,7 +2609,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" s="8">
         <v>42004</v>
       </c>
@@ -2604,7 +2620,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E84" s="12">
         <v>2.5999999999999999E-2</v>
@@ -2619,7 +2635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" s="8">
         <v>42004</v>
       </c>
@@ -2630,7 +2646,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E85" s="12">
         <v>2.1999999999999999E-2</v>
@@ -2645,7 +2661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" s="8">
         <v>42004</v>
       </c>
@@ -2656,7 +2672,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E86" s="12">
         <v>2.1999999999999999E-2</v>
@@ -2668,7 +2684,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" s="8">
         <v>42094</v>
       </c>
@@ -2679,7 +2695,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E87" s="12">
         <v>2E-3</v>
@@ -2694,7 +2710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" s="8">
         <v>42094</v>
       </c>
@@ -2705,7 +2721,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E88" s="12">
         <v>-7.0000000000000001E-3</v>
@@ -2720,7 +2736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" s="8">
         <v>42094</v>
       </c>
@@ -2731,7 +2747,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E89" s="12">
         <v>-2E-3</v>
@@ -2743,7 +2759,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" s="8">
         <v>42185</v>
       </c>
@@ -2754,7 +2770,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E90" s="12">
         <v>2.3E-2</v>
@@ -2769,7 +2785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" s="8">
         <v>42185</v>
       </c>
@@ -2780,7 +2796,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E91" s="12">
         <v>3.6999999999999998E-2</v>
@@ -2795,7 +2811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" s="8">
         <v>42185</v>
       </c>
@@ -2806,7 +2822,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E92" s="12">
         <v>3.9E-2</v>
@@ -2818,7 +2834,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" s="8">
         <v>42277</v>
       </c>
@@ -2829,7 +2845,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E93" s="12">
         <v>1.4999999999999999E-2</v>
@@ -2844,7 +2860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" s="8">
         <v>42277</v>
       </c>
@@ -2855,7 +2871,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E94" s="12">
         <v>2.1000000000000001E-2</v>
@@ -2870,7 +2886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" s="8">
         <v>42277</v>
       </c>
@@ -2881,7 +2897,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E95" s="12">
         <v>0.02</v>
@@ -2893,7 +2909,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" s="8">
         <v>42369</v>
       </c>
@@ -2904,7 +2920,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E96" s="12">
         <v>7.0000000000000001E-3</v>
@@ -2919,7 +2935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" s="8">
         <v>42369</v>
       </c>
@@ -2930,7 +2946,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E97" s="12">
         <v>0.01</v>
@@ -2945,7 +2961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" s="8">
         <v>42369</v>
       </c>
@@ -2956,7 +2972,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E98" s="12">
         <v>1.4E-2</v>
@@ -2968,7 +2984,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" s="8">
         <v>42460</v>
       </c>
@@ -2979,7 +2995,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E99" s="12">
         <v>5.0000000000000001E-3</v>
@@ -2994,7 +3010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" s="8">
         <v>42460</v>
       </c>
@@ -3005,7 +3021,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E100" s="12">
         <v>8.0000000000000002E-3</v>
@@ -3020,7 +3036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" s="8">
         <v>42460</v>
       </c>
@@ -3031,7 +3047,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E101" s="12">
         <v>1.0999999999999999E-2</v>
@@ -3043,7 +3059,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" s="8">
         <v>42551</v>
       </c>
@@ -3054,7 +3070,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E102" s="12">
         <v>1.2E-2</v>
@@ -3069,7 +3085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" s="8">
         <v>42551</v>
       </c>
@@ -3080,7 +3096,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E103" s="12">
         <v>1.0999999999999999E-2</v>
@@ -3095,7 +3111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" s="8">
         <v>42551</v>
       </c>
@@ -3106,7 +3122,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E104" s="12">
         <v>1.4E-2</v>
@@ -3118,7 +3134,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" s="8">
         <v>42643</v>
       </c>
@@ -3129,7 +3145,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E105" s="12">
         <v>2.9000000000000001E-2</v>
@@ -3144,7 +3160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" s="8">
         <v>42643</v>
       </c>
@@ -3155,7 +3171,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E106" s="12">
         <v>3.2000000000000001E-2</v>
@@ -3170,7 +3186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" s="8">
         <v>42643</v>
       </c>
@@ -3181,7 +3197,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E107" s="12">
         <v>3.5000000000000003E-2</v>
@@ -3193,7 +3209,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" s="8">
         <v>42735</v>
       </c>
@@ -3204,7 +3220,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E108" s="12">
         <v>1.9E-2</v>
@@ -3219,7 +3235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109" s="8">
         <v>42735</v>
       </c>
@@ -3230,7 +3246,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E109" s="12">
         <v>1.9E-2</v>
@@ -3245,7 +3261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" s="8">
         <v>42735</v>
       </c>
@@ -3256,7 +3272,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E110" s="12">
         <v>2.1000000000000001E-2</v>
@@ -3268,7 +3284,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" s="8">
         <v>42825</v>
       </c>
@@ -3279,7 +3295,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E111" s="12">
         <v>7.0000000000000001E-3</v>
@@ -3294,7 +3310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" s="8">
         <v>42825</v>
       </c>
@@ -3305,7 +3321,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E112" s="12">
         <v>1.2E-2</v>
@@ -3320,7 +3336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" s="8">
         <v>42825</v>
       </c>
@@ -3331,7 +3347,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E113" s="12">
         <v>1.4E-2</v>
@@ -3343,7 +3359,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" s="8">
         <v>42916</v>
       </c>
@@ -3354,7 +3370,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E114" s="12">
         <v>2.5999999999999999E-2</v>
@@ -3369,7 +3385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" s="8">
         <v>42916</v>
       </c>
@@ -3380,7 +3396,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E115" s="12">
         <v>0.03</v>
@@ -3395,7 +3411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" s="8">
         <v>42916</v>
       </c>
@@ -3406,7 +3422,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E116" s="12">
         <v>3.1E-2</v>
@@ -3418,7 +3434,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" s="8">
         <v>43008</v>
       </c>
@@ -3429,7 +3445,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E117" s="12">
         <v>0.03</v>
@@ -3444,7 +3460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" s="8">
         <v>43008</v>
       </c>
@@ -3455,7 +3471,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E118" s="12">
         <v>3.3000000000000002E-2</v>
@@ -3470,7 +3486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" s="8">
         <v>43008</v>
       </c>
@@ -3481,7 +3497,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E119" s="12">
         <v>3.2000000000000001E-2</v>
@@ -3493,7 +3509,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" s="8">
         <v>43100</v>
       </c>
@@ -3504,7 +3520,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E120" s="12">
         <v>2.5999999999999999E-2</v>
@@ -3519,7 +3535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" s="8">
         <v>43100</v>
       </c>
@@ -3530,7 +3546,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E121" s="12">
         <v>2.5000000000000001E-2</v>
@@ -3545,7 +3561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" s="8">
         <v>43100</v>
       </c>
@@ -3556,7 +3572,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E122" s="12">
         <v>2.9000000000000001E-2</v>
@@ -3568,7 +3584,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" s="8">
         <v>43190</v>
       </c>
@@ -3579,7 +3595,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E123" s="12">
         <v>2.3E-2</v>
@@ -3594,7 +3610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124" s="8">
         <v>43190</v>
       </c>
@@ -3605,7 +3621,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E124" s="12">
         <v>2.1999999999999999E-2</v>
@@ -3620,7 +3636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" s="8">
         <v>43190</v>
       </c>
@@ -3631,7 +3647,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E125" s="12">
         <v>0.02</v>
@@ -3643,7 +3659,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" s="8">
         <v>43281</v>
       </c>
@@ -3654,7 +3670,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E126" s="12">
         <v>4.1000000000000002E-2</v>
@@ -3669,7 +3685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" s="8">
         <v>43281</v>
       </c>
@@ -3680,7 +3696,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E127" s="12">
         <v>4.2000000000000003E-2</v>
@@ -3695,7 +3711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" s="8">
         <v>43281</v>
       </c>
@@ -3706,7 +3722,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E128" s="12">
         <v>4.2000000000000003E-2</v>
@@ -3718,7 +3734,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" s="8">
         <v>43373</v>
       </c>
@@ -3729,7 +3745,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E129" s="12">
         <v>3.5000000000000003E-2</v>
@@ -3744,7 +3760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A130" s="8">
         <v>43373</v>
       </c>
@@ -3755,7 +3771,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E130" s="12">
         <v>3.5000000000000003E-2</v>
@@ -3770,7 +3786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" s="8">
         <v>43373</v>
       </c>
@@ -3781,7 +3797,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E131" s="12">
         <v>3.4000000000000002E-2</v>
@@ -3793,7 +3809,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132" s="8">
         <v>43465</v>
       </c>
@@ -3804,7 +3820,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E132" s="12">
         <v>2.5999999999999999E-2</v>
@@ -3819,7 +3835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133" s="8">
         <v>43465</v>
       </c>
@@ -3830,7 +3846,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E133" s="12">
         <v>2.1999999999999999E-2</v>
@@ -3842,7 +3858,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134" s="8">
         <v>43555</v>
       </c>
@@ -3853,7 +3869,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E134" s="12">
         <v>3.2000000000000001E-2</v>
@@ -3868,7 +3884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" s="8">
         <v>43555</v>
       </c>
@@ -3879,7 +3895,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E135" s="12">
         <v>3.1E-2</v>
@@ -3894,7 +3910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" s="8">
         <v>43555</v>
       </c>
@@ -3905,7 +3921,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E136" s="12">
         <v>3.1E-2</v>
@@ -3917,7 +3933,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137" s="8">
         <v>43646</v>
       </c>
@@ -3928,7 +3944,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E137" s="12">
         <v>2.1000000000000001E-2</v>
@@ -3943,7 +3959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138" s="8">
         <v>43646</v>
       </c>
@@ -3954,7 +3970,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E138" s="12">
         <v>0.02</v>
@@ -3969,7 +3985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A139" s="8">
         <v>43646</v>
       </c>
@@ -3980,7 +3996,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E139" s="12">
         <v>0.02</v>
@@ -3992,7 +4008,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A140" s="8">
         <v>43738</v>
       </c>
@@ -4003,7 +4019,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E140" s="12">
         <v>1.9E-2</v>
@@ -4018,7 +4034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141" s="8">
         <v>43738</v>
       </c>
@@ -4029,7 +4045,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E141" s="12">
         <v>2.1000000000000001E-2</v>
@@ -4044,7 +4060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A142" s="8">
         <v>43738</v>
       </c>
@@ -4055,7 +4071,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E142" s="12">
         <v>2.1000000000000001E-2</v>
@@ -4067,7 +4083,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143" s="8">
         <v>43830</v>
       </c>
@@ -4078,7 +4094,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E143" s="12">
         <v>2.1000000000000001E-2</v>
@@ -4093,7 +4109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" s="8">
         <v>43830</v>
       </c>
@@ -4104,7 +4120,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E144" s="12">
         <v>2.1000000000000001E-2</v>
@@ -4119,7 +4135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A145" s="8">
         <v>43830</v>
       </c>
@@ -4130,7 +4146,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E145" s="12">
         <v>2.1000000000000001E-2</v>
@@ -4142,7 +4158,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146" s="8">
         <v>43921</v>
       </c>
@@ -4153,7 +4169,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E146" s="12">
         <v>-4.8000000000000001E-2</v>
@@ -4168,7 +4184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147" s="8">
         <v>43921</v>
       </c>
@@ -4179,7 +4195,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E147" s="12">
         <v>-0.05</v>
@@ -4194,7 +4210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148" s="8">
         <v>43921</v>
       </c>
@@ -4205,7 +4221,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E148" s="12">
         <v>-0.05</v>
@@ -4217,7 +4233,7 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A149" s="8">
         <v>44012</v>
       </c>
@@ -4228,7 +4244,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E149" s="12">
         <v>-0.32900000000000001</v>
@@ -4243,7 +4259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150" s="8">
         <v>44012</v>
       </c>
@@ -4254,7 +4270,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E150" s="12">
         <v>-0.317</v>
@@ -4269,7 +4285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A151" s="8">
         <v>44012</v>
       </c>
@@ -4280,7 +4296,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E151" s="12">
         <v>-0.314</v>
@@ -4292,7 +4308,7 @@
         <v>-0.317</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A152" s="8">
         <v>44104</v>
       </c>
@@ -4303,7 +4319,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E152" s="12">
         <v>0.33100000000000002</v>
@@ -4318,7 +4334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A153" s="8">
         <v>44104</v>
       </c>
@@ -4329,7 +4345,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E153" s="12">
         <v>0.33100000000000002</v>
@@ -4344,7 +4360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A154" s="8">
         <v>44104</v>
       </c>
@@ -4355,7 +4371,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E154" s="12">
         <v>0.33400000000000002</v>
@@ -4367,7 +4383,7 @@
         <v>0.33100000000000002</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155" s="8">
         <v>44196</v>
       </c>
@@ -4378,7 +4394,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E155" s="12">
         <v>0.04</v>
@@ -4393,7 +4409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156" s="8">
         <v>44196</v>
       </c>
@@ -4404,7 +4420,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E156" s="12">
         <v>4.1000000000000002E-2</v>
@@ -4419,7 +4435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A157" s="8">
         <v>44196</v>
       </c>
@@ -4430,7 +4446,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E157" s="12">
         <v>4.2999999999999997E-2</v>
@@ -4442,7 +4458,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A158" s="8">
         <v>44286</v>
       </c>
@@ -4453,7 +4469,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E158" s="12">
         <v>6.4000000000000001E-2</v>
@@ -4468,7 +4484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A159" s="8">
         <v>44286</v>
       </c>
@@ -4479,7 +4495,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E159" s="12">
         <v>6.4000000000000001E-2</v>
@@ -4494,7 +4510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A160" s="8">
         <v>44286</v>
       </c>
@@ -4505,7 +4521,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E160" s="12">
         <v>6.4000000000000001E-2</v>
@@ -4517,7 +4533,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A161" s="8">
         <v>44377</v>
       </c>
@@ -4528,7 +4544,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E161" s="12">
         <v>6.5000000000000002E-2</v>
@@ -4543,7 +4559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A162" s="8">
         <v>44377</v>
       </c>
@@ -4554,7 +4570,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E162" s="12">
         <v>6.6000000000000003E-2</v>
@@ -4569,7 +4585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A163" s="8">
         <v>44377</v>
       </c>
@@ -4580,7 +4596,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E163" s="12">
         <v>6.7000000000000004E-2</v>
@@ -4592,7 +4608,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A164" s="8">
         <v>44469</v>
       </c>
@@ -4603,7 +4619,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E164" s="12">
         <v>0.02</v>
@@ -4618,7 +4634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A165" s="8">
         <v>44469</v>
       </c>
@@ -4629,7 +4645,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E165" s="12">
         <v>2.1000000000000001E-2</v>
@@ -4644,7 +4660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A166" s="8">
         <v>44469</v>
       </c>
@@ -4655,7 +4671,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E166" s="12">
         <v>2.3E-2</v>
@@ -4667,7 +4683,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A167" s="8">
         <v>44561</v>
       </c>
@@ -4678,7 +4694,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E167" s="12">
         <v>6.9000000000000006E-2</v>
@@ -4693,7 +4709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A168" s="8">
         <v>44561</v>
       </c>
@@ -4704,7 +4720,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E168" s="12">
         <v>7.0000000000000007E-2</v>
@@ -4719,7 +4735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A169" s="8">
         <v>44561</v>
       </c>
@@ -4730,7 +4746,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E169" s="12">
         <v>6.9000000000000006E-2</v>
@@ -4742,7 +4758,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A170" s="8">
         <v>44651</v>
       </c>
@@ -4753,7 +4769,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E170" s="12">
         <v>-1.4E-2</v>
@@ -4768,7 +4784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A171" s="8">
         <v>44651</v>
       </c>
@@ -4779,7 +4795,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D171" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E171" s="12">
         <v>-1.4999999999999999E-2</v>
@@ -4794,7 +4810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A172" s="8">
         <v>44651</v>
       </c>
@@ -4805,7 +4821,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E172" s="12">
         <v>-1.6E-2</v>
@@ -4817,7 +4833,7 @@
         <v>-1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A173" s="8">
         <v>44742</v>
       </c>
@@ -4828,7 +4844,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E173" s="12">
         <v>-8.9999999999999993E-3</v>
@@ -4843,7 +4859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A174" s="8">
         <v>44742</v>
       </c>
@@ -4854,7 +4870,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E174" s="12">
         <v>-6.0000000000000001E-3</v>
@@ -4869,7 +4885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A175" s="8">
         <v>44742</v>
       </c>
@@ -4880,7 +4896,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D175" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E175" s="12">
         <v>-6.0000000000000001E-3</v>
@@ -4892,7 +4908,7 @@
         <v>-1.6E-2</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A176" s="8">
         <v>44834</v>
       </c>
@@ -4903,7 +4919,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E176" s="12">
         <v>2.5999999999999999E-2</v>
@@ -4918,7 +4934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A177" s="8">
         <v>44834</v>
       </c>
@@ -4929,7 +4945,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E177" s="12">
         <v>2.9000000000000001E-2</v>
@@ -4944,7 +4960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A178" s="8">
         <v>44834</v>
       </c>
@@ -4955,7 +4971,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E178" s="12">
         <v>3.2000000000000001E-2</v>
@@ -4967,7 +4983,7 @@
         <v>-6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A179" s="8">
         <v>44926</v>
       </c>
@@ -4978,7 +4994,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E179" s="12">
         <v>2.9000000000000001E-2</v>
@@ -4993,7 +5009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A180" s="8">
         <v>44926</v>
       </c>
@@ -5004,7 +5020,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E180" s="12">
         <v>2.7E-2</v>
@@ -5019,7 +5035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A181" s="8">
         <v>44926</v>
       </c>
@@ -5030,7 +5046,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E181" s="12">
         <v>2.5999999999999999E-2</v>
@@ -5042,7 +5058,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A182" s="8">
         <v>45016</v>
       </c>
@@ -5053,7 +5069,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E182" s="12">
         <v>1.0999999999999999E-2</v>
@@ -5068,7 +5084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A183" s="8">
         <v>45016</v>
       </c>
@@ -5079,7 +5095,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E183" s="12">
         <v>1.2999999999999999E-2</v>
@@ -5094,7 +5110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A184" s="8">
         <v>45016</v>
       </c>
@@ -5105,7 +5121,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E184" s="12">
         <v>0.02</v>
@@ -5117,7 +5133,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A185" s="8">
         <v>45107</v>
       </c>
@@ -5128,7 +5144,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E185" s="12">
         <v>2.4E-2</v>
@@ -5143,7 +5159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A186" s="8">
         <v>45107</v>
       </c>
@@ -5154,7 +5170,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E186" s="12">
         <v>2.1000000000000001E-2</v>
@@ -5169,7 +5185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A187" s="8">
         <v>45107</v>
       </c>
@@ -5180,7 +5196,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E187" s="12">
         <v>2.1000000000000001E-2</v>
@@ -5192,7 +5208,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A188" s="8">
         <v>45199</v>
       </c>
@@ -5203,7 +5219,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E188" s="12">
         <v>4.9000000000000002E-2</v>
@@ -5218,7 +5234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A189" s="8">
         <v>45199</v>
       </c>
@@ -5229,7 +5245,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E189" s="12">
         <v>5.1999999999999998E-2</v>
@@ -5244,7 +5260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A190" s="8">
         <v>45199</v>
       </c>
@@ -5255,7 +5271,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E190" s="12">
         <v>4.9000000000000002E-2</v>
@@ -5267,7 +5283,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A191" s="8">
         <v>45291</v>
       </c>
@@ -5278,7 +5294,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E191" s="12">
         <v>3.3000000000000002E-2</v>
@@ -5293,7 +5309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A192" s="8">
         <v>45291</v>
       </c>
@@ -5304,7 +5320,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E192" s="12">
         <v>3.2000000000000001E-2</v>
@@ -5319,7 +5335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A193" s="8">
         <v>45291</v>
       </c>
@@ -5330,7 +5346,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E193" s="12">
         <v>3.4000000000000002E-2</v>
@@ -5342,7 +5358,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A194" s="8">
         <v>45382</v>
       </c>
@@ -5353,7 +5369,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E194" s="12">
         <v>1.6E-2</v>
@@ -5368,7 +5384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A195" s="8">
         <v>45382</v>
       </c>
@@ -5379,7 +5395,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E195" s="12">
         <v>1.2999999999999999E-2</v>
@@ -5394,7 +5410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A196" s="8">
         <v>45382</v>
       </c>
@@ -5405,7 +5421,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E196" s="12">
         <v>1.4E-2</v>
@@ -5417,7 +5433,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A197" s="8">
         <v>45473</v>
       </c>
@@ -5428,7 +5444,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E197" s="12">
         <v>2.8000000000000001E-2</v>
@@ -5443,7 +5459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A198" s="8">
         <v>45473</v>
       </c>
@@ -5454,7 +5470,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E198" s="12">
         <v>0.03</v>
@@ -5469,7 +5485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A199" s="8">
         <v>45473</v>
       </c>
@@ -5480,7 +5496,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E199" s="12">
         <v>0.03</v>
@@ -5492,7 +5508,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A200" s="8">
         <v>45565</v>
       </c>
@@ -5503,7 +5519,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E200" s="12">
         <v>2.8000000000000001E-2</v>
@@ -5518,7 +5534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A201" s="8">
         <v>45565</v>
       </c>
@@ -5529,7 +5545,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D201" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E201" s="12">
         <v>2.8000000000000001E-2</v>
@@ -5544,7 +5560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A202" s="8">
         <v>45565</v>
       </c>
@@ -5555,7 +5571,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E202" s="12">
         <v>3.1E-2</v>
@@ -5567,7 +5583,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A203" s="8">
         <v>45657</v>
       </c>
@@ -5578,7 +5594,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E203" s="12">
         <v>2.3E-2</v>
@@ -5593,7 +5609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A204" s="8">
         <v>45657</v>
       </c>
@@ -5604,7 +5620,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E204" s="12">
         <v>2.3E-2</v>
@@ -5619,7 +5635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A205" s="8">
         <v>45657</v>
       </c>
@@ -5630,7 +5646,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E205" s="12">
         <v>2.4E-2</v>
@@ -5642,7 +5658,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A206" s="8">
         <v>45747</v>
       </c>
@@ -5653,7 +5669,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E206" s="12">
         <v>-3.0000000000000001E-3</v>
@@ -5668,7 +5684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A207" s="8">
         <v>45747</v>
       </c>
@@ -5679,7 +5695,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E207" s="12">
         <v>-2E-3</v>
@@ -5694,7 +5710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A208" s="8">
         <v>45747</v>
       </c>
@@ -5705,7 +5721,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D208" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E208" s="12">
         <v>-5.0000000000000001E-3</v>
@@ -5717,7 +5733,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A209" s="8">
         <v>45838</v>
       </c>
@@ -5728,7 +5744,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E209" s="12">
         <v>0.03</v>
@@ -5743,7 +5759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A210" s="8">
         <v>45838</v>
       </c>
@@ -5754,7 +5770,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E210" s="12">
         <v>3.3000000000000002E-2</v>
@@ -5769,7 +5785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A211" s="8">
         <v>45838</v>
       </c>
@@ -5780,7 +5796,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E211" s="12">
         <v>3.7999999999999999E-2</v>
@@ -5792,7 +5808,7 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A212" s="8">
         <v>45930</v>
       </c>
@@ -5803,7 +5819,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D212" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E212" s="12">
         <v>4.2999999999999997E-2</v>
@@ -5818,7 +5834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A213" s="8">
         <v>45930</v>
       </c>
@@ -5829,7 +5845,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E213" s="12">
         <v>4.3999999999999997E-2</v>
@@ -5841,7 +5857,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A214" s="8">
         <v>46022</v>
       </c>
@@ -5852,7 +5868,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E214" s="12">
         <v>1.4E-2</v>
@@ -5867,8 +5883,57 @@
         <v>1</v>
       </c>
     </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A215" s="8">
+        <v>46022</v>
+      </c>
+      <c r="B215" s="8">
+        <v>46094</v>
+      </c>
+      <c r="C215" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D215" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E215" s="12">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="F215" s="12">
+        <v>1.4E-2</v>
+      </c>
+      <c r="G215" s="12">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="H215" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A216" s="8">
+        <v>46022</v>
+      </c>
+      <c r="B216" s="8">
+        <v>46121</v>
+      </c>
+      <c r="C216" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D216" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E216" s="12">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F216" s="12">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="G216" s="12">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="B2:H212">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:H212">
     <sortCondition descending="1" ref="H2:H212"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -5880,18 +5945,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E588249D-97CE-469E-B7B2-E86F8F097470}">
   <dimension ref="B2:C2"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
+      <c r="C2" s="13" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{54CE3A5A-3A6D-4AED-B841-119622AA13D4}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/macro/USA/USGDP.xlsx
+++ b/data/macro/USA/USGDP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E9FB8D-DCC5-4A8B-B095-013A5E4CFB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F301442-3441-438F-AF71-AB92FEE58EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF730CA5-B386-4F44-87DF-4B36E64B9A15}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="12">
   <si>
     <t>Release Date</t>
   </si>
@@ -522,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00FCE0E7-6C64-48A0-8BF6-812467A264DB}">
-  <dimension ref="A1:H216"/>
+  <dimension ref="A1:H217"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="14.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -5930,6 +5930,32 @@
       </c>
       <c r="G216" s="12">
         <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A217" s="8">
+        <v>46112</v>
+      </c>
+      <c r="B217" s="8">
+        <v>46142</v>
+      </c>
+      <c r="C217" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D217" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E217" s="12">
+        <v>0.02</v>
+      </c>
+      <c r="F217" s="12">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="G217" s="12">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H217" s="7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
